--- a/data/reports/report-2026-07-27.xlsx
+++ b/data/reports/report-2026-07-27.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -696,17 +696,17 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>626620</v>
+        <v>626704</v>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="5" t="n">
-        <v>576470</v>
+        <v>576498</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>559921</v>
+        <v>559933</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>471127</v>
+        <v>471129</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -721,17 +721,17 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>518466</v>
+        <v>518382</v>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="5" t="n">
-        <v>435424</v>
+        <v>435396</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>478218</v>
+        <v>478206</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>452210</v>
+        <v>452207</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
@@ -779,17 +779,17 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>461772</v>
+        <v>461688</v>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
       <c r="D10" s="5" t="n">
-        <v>385129</v>
+        <v>385101</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>426246</v>
+        <v>426234</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>406759</v>
+        <v>406756</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -864,22 +864,22 @@
         <v>479375</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>626620</v>
+        <v>626704</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>518466</v>
+        <v>518382</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.3192</v>
+        <v>0.3191</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>56694</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>461772</v>
+        <v>461688</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.2843</v>
+        <v>0.2842</v>
       </c>
     </row>
     <row r="15">
@@ -895,10 +895,10 @@
         <v>1287738</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1729409</v>
+        <v>1729493</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1306273</v>
+        <v>1306189</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>0.3021</v>
@@ -907,7 +907,7 @@
         <v>150887</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1155386</v>
+        <v>1155302</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.2672</v>
@@ -926,10 +926,10 @@
         <v>3157189</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>3919446</v>
+        <v>3919530</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>3347527</v>
+        <v>3347443</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>0.3211</v>
@@ -938,7 +938,7 @@
         <v>363803</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2983724</v>
+        <v>2983640</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.2862</v>
@@ -957,10 +957,10 @@
         <v>11369539</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>14133800</v>
+        <v>14133884</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>13566306</v>
+        <v>13566222</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>0.3472</v>
@@ -969,7 +969,7 @@
         <v>1363531</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>12202775</v>
+        <v>12202691</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.3123</v>
@@ -982,28 +982,28 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>16290866</v>
+        <v>13041944</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>4887073</v>
+        <v>3916512</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>6201349</v>
+        <v>4948380</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>5202444</v>
+        <v>4177052</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.3193</v>
+        <v>0.3203</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>568551</v>
+        <v>455164</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>4633893</v>
+        <v>3721888</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.2844</v>
+        <v>0.2854</v>
       </c>
     </row>
     <row r="20">
@@ -1080,6 +1080,27 @@
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>・★増額候補（自分の目標MER超え × 消化率95%以上）: 4WAY 取り付けOK (3.73&gt;3.30・103%)・害虫ブロッカー(2.91&gt;2.31・100%)・形状記憶日傘(3.44&gt;2.58・98%)・ナノガラス脱毛パッド(2.51&gt;2.17・100%)・卓上冷感クーラー(3.73&gt;3.16・98%)・5WAY腰掛けファン(4.59&gt;3.59・102%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>・⚠️訂正: 7/27朝に一度お渡ししたファイルの「7/18〜累積」行が誤っていました（売上16,290,866円等）。累積を繰り越しファイルへの加算方式で作っていたため、生成スクリプトを3回走らせた分だけ7/26が3重計上されていました。本ファイルは累積を日次実測から毎回積み直す方式に変更し、日次合計との一致を自動チェックしています（他の行は元から毎回再計算のため影響なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>・★全店の広告費をキャンペーン合算からMetaのアカウントレベル日次実測に変更（取りこぼしが構造的に起きない）。差は7日で84円</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>・★7/18〜累積の原価は全日を現行（7/25改定後）の原価表で評価している。前回ファイルの8日累積3,448,948円との差−11,811円は、この基準統一とディスペンサーのバリエーション別原価の修正による</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3195,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>ナノバブルシャワーヘッド</t>
+          <t>ネックマッサージャー</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
@@ -3219,7 +3240,7 @@
       </c>
       <c r="R24" s="4" t="inlineStr"/>
       <c r="S24" s="6" t="n">
-        <v>51975</v>
+        <v>6946</v>
       </c>
       <c r="T24" s="4" t="inlineStr"/>
       <c r="U24" s="4" t="inlineStr"/>
@@ -3245,7 +3266,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>リカバリーサンダル</t>
+          <t>姿勢サポートベルト</t>
         </is>
       </c>
       <c r="B25" s="16" t="n">
@@ -3290,7 +3311,7 @@
       </c>
       <c r="R25" s="15" t="inlineStr"/>
       <c r="S25" s="16" t="n">
-        <v>18697</v>
+        <v>4551</v>
       </c>
       <c r="T25" s="15" t="inlineStr"/>
       <c r="U25" s="15" t="inlineStr"/>
@@ -3316,7 +3337,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>ネックマッサージャー</t>
+          <t>ナノバブルシャワーヘッド</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
@@ -3361,7 +3382,7 @@
       </c>
       <c r="R26" s="4" t="inlineStr"/>
       <c r="S26" s="6" t="n">
-        <v>6946</v>
+        <v>51975</v>
       </c>
       <c r="T26" s="4" t="inlineStr"/>
       <c r="U26" s="4" t="inlineStr"/>
@@ -3387,7 +3408,7 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>姿勢サポートベルト</t>
+          <t>リカバリーサンダル</t>
         </is>
       </c>
       <c r="B27" s="16" t="n">
@@ -3432,7 +3453,7 @@
       </c>
       <c r="R27" s="15" t="inlineStr"/>
       <c r="S27" s="16" t="n">
-        <v>4551</v>
+        <v>18697</v>
       </c>
       <c r="T27" s="15" t="inlineStr"/>
       <c r="U27" s="15" t="inlineStr"/>

--- a/data/reports/report-2026-07-27.xlsx
+++ b/data/reports/report-2026-07-27.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="全体サマリー" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="商品別" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="判定フロー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ネクストアクション" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="全体サマリー" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="商品別" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="判定フロー" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,12 +34,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="13"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -49,6 +51,16 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -112,12 +124,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F6FC"/>
+        <fgColor rgb="00D6EFD8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EFD8"/>
+        <fgColor rgb="00F2F6FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,54 +164,58 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -572,6 +588,876 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LOOTY ネクストアクション 2026-07-27(月) 定例（昨日=7/26 日実績）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>■ 今日やること（広告）※すべて本日実施済み</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>現→提案</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>所要</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>卓上冷感クーラー 日予算を戻す</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>38,000→30,000</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2分</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>7/25の増額分の増分MER −9.5（分岐1.50）</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>✅実施済</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>害虫ブロッカー本体にCRを追加</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>70,000（据置）</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>CTR 3.28%→2.68%（−18%）・配信CR1本</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>✅実施済（０７１９のB/Aを投入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>4WAY の複製リセット</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>95,000（据置）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>当初CR1本のため予備。ただし下記の理由で不要と再判定</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>⏹ 取り下げ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>■ 今週の1件（広告以外）</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>作業</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>所要</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>期待効果</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>卓上冷感クーラー</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>①カラー/タイプのバリエーション追加（現在Default Title 1種のみ）</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>7/31</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>CVR 1.93%→2.5%で +170,244円/週</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>8/3 CVR≥2.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>卓上冷感クーラー</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>②FVに「水を入れる家電」の不安解消ブロックを追加</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>1時間</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>残シーズン5週。1週遅れるごとに約170,000円の機会損失</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>✅本日実施済</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>ムダ毛シェーバー</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>価格 5,980→6,980円（5分で終わる別枠）</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>+26,181〜45,000円/週（通年）</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>8/3 7日販売数≥35個</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>✅実施済</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>■ 4WAY にCRが不要な理由（診断の訂正）</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>W1(7/13-19)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>W2(7/20-26)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>変化</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>インプレッション</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>71,223</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>125,663</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>+76.4%</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>頻度</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>1.568</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>1.570</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>±0.0</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>← 擦り切れていない</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>CPM</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>5,519</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>4,780</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>−13.4%</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>← 安い配信面に降りている</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>5.82%</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>−15.6%</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>診断</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>素材疲弊ではなく「予算増による配信面の拡大」。CRでは直らず、正しい対処は予算を戻すこと（7/28判定）</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>■ 次の判定日（基準は宣言済み。当日は当てはめるだけ）</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>合格基準</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>不合格時</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>4WAY</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>増分MER ≥ 1.53</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>95,000→85,000</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>完全遮光・UV日傘</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>増分MER ≥ 1.35</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>41,000→34,000</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>接触冷感UVパーカー</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>曜日補正・全店補正が同ゾーンに収束し ≥ 3.45</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>3.45未満=据置／1.56未満=28,000</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>5WAY腰掛けファン</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>余裕 ≥ +1.0 維持</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>据置</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>完全遮光・接触冷感UVハット</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>【新規】浮いた予算13,000円で出稿開始</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>8/4にCPA判定</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>サングラス・スリッパ・アームカバー・3WAY</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>余裕 &gt; 0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>D診断→CR/LP</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>携帯電動シェーバー</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>7日MER ≥ 1.90（8/1から前倒し）</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>11,000→8,000</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>害虫ブロッカー・ナノガラス</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>7/26増額分の増分MER ≥ 分岐（1.28 / 1.23）</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>85,000 / 68,000 を元に戻す</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>UV歯ブラシ除菌器</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>A-コピーのCPA &lt; 5,000</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>減額</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>7/31</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>秋物選定（シーズン到来3〜4週前）</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>8/3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>卓上（LP）・害虫（CR）・ムダ毛（値上げ）</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>本日実施分の効果判定</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>各上記</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>8/4</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>UVハット</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>7日CPA &lt; 2,476円→増額／&lt; 4,569円→据置／以上→停止</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>8/1</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>手数料月次再計測・ポンチョ・ディスペンサー早期判定</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>■ CVRは自店19商品の順位で見る（中央値 3.18%）※前週比だけでLP改善と判断しない</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>LP改善の対象（下位25%）</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>ディスペンサー1.42%(19位)・卓上1.93%(18位)・ワンピース2.14%(17位)・UV歯ブラシ2.60%(16位)・3WAY2.75%(15位)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>LPを触らない（中央値以上）</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>4WAY4.74%(1位)・アームカバー4.68%(2位)・パーカー4.21%(3位)・5WAY3.54%(4位)・害虫3.52%(5位)・ムダ毛3.51%(6位)・ナノ3.47%(7位)・サンダル3.39%(8位)・スリッパ3.21%(9位)・携帯シェーバー3.18%(10位)</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>訂正</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>7/27午前にスリッパ(9位)と携帯シェーバー(10位)へ出したLP改善提案は誤り。前週が異常に高かっただけで中央値以上</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr"/>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -587,518 +1473,518 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>LOOTY 日次損益レポート 2026-07-27(月) 定例（昨日=7/26 日実績）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>■ 昨日の全体実績 × 期間比較</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>昨日</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>同曜日平均</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>3日平均/日</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>7日平均/日</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>30日平均/日</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>昨日vs7日平均</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>売上(gross−値引)</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="9" t="n">
         <v>1624461</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="9" t="n">
         <v>1517203</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="9" t="n">
         <v>1441140</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="9" t="n">
         <v>1489166</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="9" t="n">
         <v>1302322</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>+9.1% ✅</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>原価</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="9" t="n">
         <v>479375</v>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="5" t="n">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="9" t="n">
         <v>429246</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="9" t="n">
         <v>451027</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="9" t="n">
         <v>378985</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>+6.3%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>広告費</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="9" t="n">
         <v>626704</v>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="5" t="n">
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="9" t="n">
         <v>576498</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="9" t="n">
         <v>559933</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="9" t="n">
         <v>471129</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>+11.9%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>利益</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="9" t="n">
         <v>518382</v>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="5" t="n">
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="9" t="n">
         <v>435396</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="9" t="n">
         <v>478206</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="9" t="n">
         <v>452207</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>+8.4%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>利益率</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>31.9%</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>30.2%</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>32.1%</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>34.7%</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>-0.2pt</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>手数料控除後利益</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="9" t="n">
         <v>461688</v>
       </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="5" t="n">
+      <c r="C10" s="8" t="inlineStr"/>
+      <c r="D10" s="9" t="n">
         <v>385101</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="9" t="n">
         <v>426234</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="9" t="n">
         <v>406756</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>+8.3%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>■ 期間別サマリー（カタログ広告費込み・全商品）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>期間</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>売上(gross−値引)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>原価</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>広告費</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>利益</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>利益率</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>手数料(3.49%)</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>控除後利益</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>控除後利益率</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>前日(7/26 日)</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="10" t="n">
         <v>1624461</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="10" t="n">
         <v>479375</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="10" t="n">
         <v>626704</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="10" t="n">
         <v>518382</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="11" t="n">
         <v>0.3191</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="10" t="n">
         <v>56694</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="10" t="n">
         <v>461688</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="11" t="n">
         <v>0.2842</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>3日(7/24-26)</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="10" t="n">
         <v>4323420</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="10" t="n">
         <v>1287738</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="10" t="n">
         <v>1729493</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="10" t="n">
         <v>1306189</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="11" t="n">
         <v>0.3021</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="10" t="n">
         <v>150887</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="10" t="n">
         <v>1155302</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="11" t="n">
         <v>0.2672</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>7日(7/20-26)</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="10" t="n">
         <v>10424162</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="10" t="n">
         <v>3157189</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="10" t="n">
         <v>3919530</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="10" t="n">
         <v>3347443</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="11" t="n">
         <v>0.3211</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="10" t="n">
         <v>363803</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="10" t="n">
         <v>2983640</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="11" t="n">
         <v>0.2862</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>30日(6/27-7/26)</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="10" t="n">
         <v>39069645</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="10" t="n">
         <v>11369539</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="10" t="n">
         <v>14133884</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="10" t="n">
         <v>13566222</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="11" t="n">
         <v>0.3472</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="10" t="n">
         <v>1363531</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="10" t="n">
         <v>12202691</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="11" t="n">
         <v>0.3123</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>📅7/18〜7/26累積(9日)</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="10" t="n">
         <v>13041944</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="10" t="n">
         <v>3916512</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="10" t="n">
         <v>4948380</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="10" t="n">
         <v>4177052</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="11" t="n">
         <v>0.3203</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="10" t="n">
         <v>455164</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="10" t="n">
         <v>3721888</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I18" s="11" t="n">
         <v>0.2854</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>・売上=gross_sales−discounts（返品A案）。当月返品累計 7/26時点 192,461円（返品率0.54%）。7/26 新規返品ゼロ</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>・★全店の週次実測: W1(7/13-19) 売上8,840,547円・広告3,325,602円・MER2.66 → W2(7/20-26) 売上10,424,162円・広告3,919,446円・MER2.66。広告+17.9%に対し売上+17.9%＝増額分は平均と同じ効率で回収できており、全店の分岐MER1.44を大きく上回る。「増額したのに売上が伸びていない」という状態ではない（完全週どうしの比較なので曜日補正は不要）</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>・★増分MERは「最後の1段」を測る。同じ商品でも 週次（ランプ全体）と P1/P2（直近の1段）で符号が逆になる。例: 卓上冷感クーラーは週次+3.29（15k→38kのランプ全体は成功）だが、直近の30,000→38,000の1段は−9.5（失敗）。予算の増減判定に使うのはP1/P2の方</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>・★P1/P2の補正を2通りで実施し、両方が同じ結論に落ちたときだけ採用する（割れたら判定保留）。①曜日指数補正 ②全店コントロール補正＝同期間の「他商品合計」の増減で割り戻す。②を追加した理由: 7/20は海の日で7/20-23の全店実績は曜日期待値の121〜127%と大きく上振れており、曜日指数だけでは補正しきれないため</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>・曜日指数(30日実測): 日116・水104・土102・金98・月95・木93・火86</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>・★S2b（機会費用）の評価式を修正: 転用先の増収は転用先の「実測の増分MER」で見積もる。平均MERで見積もると既存売上の下駄を履いた過大な転用益が出る（7/25の予算提言が外れた原因と同じ誤り）</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>・★壁掛けディスペンサーは7/25に12,000→6,000円へ半減。半減後の実績(7/25-26)は売上32,900円・原価6,490円・広告8,714円＝2日で+17,696円の黒字。7日累計が赤字なのは半減前(7/20-24)の分。半減は正解だった（増分MER 曜日+0.50/全店+0.22＝削った分は元々回収できていなかった）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>・全期間の売上・原価・広告費はShopify/Metaの実測。推計・外挿・平均の流用は不使用。ナノガラス脱毛パッド・壁掛けディスペンサーはバリエーション別の実販売数で原価を加重（30日も実測。7日構成比の流用をやめた）</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>・30日窓の途中開始: 卓上冷感クーラー7/13(14日)・5WAY腰掛けファン7/19(8日)・瞬間冷感ポンチョ/ムダ毛シェーバー7/10(17日)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>・広告セット19/21が配信CR1本（日予算合計の約92%）。害虫ブロッカー本体(70,000円)・4WAY(95,000円)が最大の単一CR依存</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>・★増額候補（自分の目標MER超え × 消化率95%以上）: 4WAY 取り付けOK (3.73&gt;3.30・103%)・害虫ブロッカー(2.91&gt;2.31・100%)・形状記憶日傘(3.44&gt;2.58・98%)・ナノガラス脱毛パッド(2.51&gt;2.17・100%)・卓上冷感クーラー(3.73&gt;3.16・98%)・5WAY腰掛けファン(4.59&gt;3.59・102%)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>・⚠️訂正: 7/27朝に一度お渡ししたファイルの「7/18〜累積」行が誤っていました（売上16,290,866円等）。累積を繰り越しファイルへの加算方式で作っていたため、生成スクリプトを3回走らせた分だけ7/26が3重計上されていました。本ファイルは累積を日次実測から毎回積み直す方式に変更し、日次合計との一致を自動チェックしています（他の行は元から毎回再計算のため影響なし）</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>・★全店の広告費をキャンペーン合算からMetaのアカウントレベル日次実測に変更（取りこぼしが構造的に起きない）。差は7日で84円</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>・★7/18〜累積の原価は全日を現行（7/25改定後）の原価表で評価している。前回ファイルの8日累積3,448,948円との差−11,811円は、この基準統一とディスペンサーのバリエーション別原価の修正による</t>
         </is>
@@ -1109,13 +1995,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA28"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1142,2406 +2028,2657 @@
     <col width="8" customWidth="1" min="22" max="22"/>
     <col width="7" customWidth="1" min="23" max="23"/>
     <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
-    <col width="52" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="62" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>商品</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>7日売上</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>7日原価</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>7日広告費</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>7日利益</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>7日利益率</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>原価率</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>広告費率</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>3日売上</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>3日原価</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>3日広告費</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>3日利益</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>3日利益率</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>前日売上</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>前日原価</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>前日広告費</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>前日利益</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>前日利益率</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>30日利益</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>MER(7日)</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>分岐</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>目標MER</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>余裕</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>増分MER</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>CVR(7日)</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
+          <t>CVR順位</t>
+        </is>
+      </c>
+      <c r="AA1" s="4" t="inlineStr">
+        <is>
+          <t>残シーズン(週)</t>
+        </is>
+      </c>
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>現日予算(円)</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>推奨アクション</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>4WAY 取り付けOK 小型瞬間冷却ハンディファン</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="10" t="n">
         <v>2241000</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="10" t="n">
         <v>778500</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="10" t="n">
         <v>600668</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="10" t="n">
         <v>861832</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="F2" s="11" t="n">
         <v>0.3846</v>
       </c>
-      <c r="G2" s="9" t="n">
+      <c r="G2" s="13" t="n">
         <v>0.3474</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="H2" s="11" t="n">
         <v>0.268</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" s="10" t="n">
         <v>831660</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="J2" s="10" t="n">
         <v>288910</v>
       </c>
-      <c r="K2" s="6" t="n">
+      <c r="K2" s="10" t="n">
         <v>279522</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="L2" s="10" t="n">
         <v>263228</v>
       </c>
-      <c r="M2" s="7" t="n">
+      <c r="M2" s="11" t="n">
         <v>0.3165</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="N2" s="10" t="n">
         <v>263940</v>
       </c>
-      <c r="O2" s="6" t="n">
+      <c r="O2" s="10" t="n">
         <v>91690</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="P2" s="10" t="n">
         <v>108917</v>
       </c>
-      <c r="Q2" s="6" t="n">
+      <c r="Q2" s="10" t="n">
         <v>63333</v>
       </c>
-      <c r="R2" s="10" t="n">
+      <c r="R2" s="14" t="n">
         <v>0.24</v>
       </c>
-      <c r="S2" s="6" t="n">
+      <c r="S2" s="10" t="n">
         <v>2718353</v>
       </c>
-      <c r="T2" s="11" t="n">
+      <c r="T2" s="15" t="n">
         <v>3.73</v>
       </c>
-      <c r="U2" s="12" t="n">
+      <c r="U2" s="16" t="n">
         <v>1.53</v>
       </c>
-      <c r="V2" s="12" t="n">
+      <c r="V2" s="16" t="n">
         <v>3.3</v>
       </c>
-      <c r="W2" s="12" t="n">
+      <c r="W2" s="16" t="n">
         <v>2.2</v>
       </c>
-      <c r="X2" s="13" t="n">
+      <c r="X2" s="17" t="n">
         <v>-3.38</v>
       </c>
-      <c r="Y2" s="6" t="n">
+      <c r="Y2" s="18" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="Z2" s="8" t="inlineStr">
+        <is>
+          <t>1位/19</t>
+        </is>
+      </c>
+      <c r="AA2" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB2" s="10" t="n">
         <v>95000</v>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AC2" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA2" s="14" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 7/28） ／ 【診断】D1素材疲弊・D3 LP/オファー（CTR 5.82%→4.91% (-16%) / CVR 5.7%→4.7% (-17%)） ／ 【CR】4WAY（95,000円）は配信CR1本のみ。予備CRを追加（既存は止めない） ／ 【LP】FV・レビュー・配送日数を見直し。優先配送の訴求位置も ／ 【原価】原価率34.7%&gt;33%。CJに数量交渉／【価格】+1,000円で数量−23.5%まで許容 ／ 【増分MER実測】週次+1.44 / 曜日-3.74 / 全店-3.02（曜日・全店の2手法が一致→採用）</t>
+      <c r="AD2" s="5" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 7/28） ／ 【診断】D3 LP/オファー・D1a 配信面の拡大（予算増が原因・CRでは直らない）（CTR 5.82%→4.91% (-16%) / CVR 5.7%→4.7% (-17%) / インプ+76%・頻度+0%・CPM-13%） ／ 【CR】4WAY（95,000円）は配信CR1本だが、劣化原因が配信面の拡大のためCR追加では直らない→予算で対処 ／ 【LP】CVR 4.74%＝自店1位/19。中央値以上なのでLPは触らない ／ 【価格】原価率34.7%&gt;33%。残シーズン5週なので原価交渉は間に合わない→値上げのみ。+1,000円で数量−23.5%まで許容 ／ 【増分MER実測】週次+1.44 / 曜日-3.74 / 全店-3.02（曜日・全店の2手法が一致→採用）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>害虫ブロッカー</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="21" t="n">
         <v>1508420</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="21" t="n">
         <v>327726</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="21" t="n">
         <v>518623</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="21" t="n">
         <v>662071</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="22" t="n">
         <v>0.4389</v>
       </c>
-      <c r="G3" s="17" t="n">
+      <c r="G3" s="22" t="n">
         <v>0.2173</v>
       </c>
-      <c r="H3" s="17" t="n">
+      <c r="H3" s="22" t="n">
         <v>0.3438</v>
       </c>
-      <c r="I3" s="16" t="n">
+      <c r="I3" s="21" t="n">
         <v>692520</v>
       </c>
-      <c r="J3" s="16" t="n">
+      <c r="J3" s="21" t="n">
         <v>150858</v>
       </c>
-      <c r="K3" s="16" t="n">
+      <c r="K3" s="21" t="n">
         <v>230411</v>
       </c>
-      <c r="L3" s="16" t="n">
+      <c r="L3" s="21" t="n">
         <v>311251</v>
       </c>
-      <c r="M3" s="17" t="n">
+      <c r="M3" s="22" t="n">
         <v>0.4494</v>
       </c>
-      <c r="N3" s="16" t="n">
+      <c r="N3" s="21" t="n">
         <v>270640</v>
       </c>
-      <c r="O3" s="16" t="n">
+      <c r="O3" s="21" t="n">
         <v>58956</v>
       </c>
-      <c r="P3" s="16" t="n">
+      <c r="P3" s="21" t="n">
         <v>81454</v>
       </c>
-      <c r="Q3" s="16" t="n">
+      <c r="Q3" s="21" t="n">
         <v>130230</v>
       </c>
-      <c r="R3" s="17" t="n">
+      <c r="R3" s="22" t="n">
         <v>0.4812</v>
       </c>
-      <c r="S3" s="16" t="n">
+      <c r="S3" s="21" t="n">
         <v>3925528</v>
       </c>
-      <c r="T3" s="11" t="n">
+      <c r="T3" s="15" t="n">
         <v>2.91</v>
       </c>
-      <c r="U3" s="18" t="n">
+      <c r="U3" s="23" t="n">
         <v>1.28</v>
       </c>
-      <c r="V3" s="18" t="n">
+      <c r="V3" s="23" t="n">
         <v>2.31</v>
       </c>
-      <c r="W3" s="18" t="n">
+      <c r="W3" s="23" t="n">
         <v>1.63</v>
       </c>
-      <c r="X3" s="15" t="inlineStr"/>
-      <c r="Y3" s="16" t="n">
+      <c r="X3" s="20" t="inlineStr"/>
+      <c r="Y3" s="18" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="Z3" s="20" t="inlineStr">
+        <is>
+          <t>5位/19</t>
+        </is>
+      </c>
+      <c r="AA3" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB3" s="21" t="n">
         <v>85000</v>
       </c>
-      <c r="Z3" s="15" t="inlineStr">
+      <c r="AC3" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA3" s="19" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 7/30） ／ 【診断】D1素材疲弊（CTR 3.28%→2.68% (-18%)） ／ 【CR】本体（70,000円）は配信CR1本のみ。予備CRを追加（既存は止めない） ／ 【増分MER実測】週次+2.43（週次のみ。直近1段のP1/P2は測定条件を満たさず＝参考値）</t>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 7/30） ／ 【診断】D1a 配信面の拡大（予算増が原因・CRでは直らない）（CTR 3.28%→2.68% (-18%) / インプ+34%・頻度+2%・CPM-10%） ／ 【CR】本体（70,000円）は配信CR1本だが、劣化原因が配信面の拡大のためCR追加では直らない→予算で対処 ／ 【LP】CVR 3.52%＝自店5位/19。中央値以上なのでLPは触らない ／ 【増分MER実測】週次+2.43（週次のみ。直近1段のP1/P2は測定条件を満たさず＝参考値）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>形状記憶日傘</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="10" t="n">
         <v>1459140</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="10" t="n">
         <v>383537</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="10" t="n">
         <v>423566</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="10" t="n">
         <v>652037</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="11" t="n">
         <v>0.4469</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="11" t="n">
         <v>0.2629</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="11" t="n">
         <v>0.2903</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="10" t="n">
         <v>622500</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="10" t="n">
         <v>163625</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="K4" s="10" t="n">
         <v>175032</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="10" t="n">
         <v>283843</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="11" t="n">
         <v>0.456</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="N4" s="10" t="n">
         <v>234060</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="O4" s="10" t="n">
         <v>61523</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="P4" s="10" t="n">
         <v>63307</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="Q4" s="10" t="n">
         <v>109230</v>
       </c>
-      <c r="R4" s="7" t="n">
+      <c r="R4" s="11" t="n">
         <v>0.4667</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="S4" s="10" t="n">
         <v>2203480</v>
       </c>
-      <c r="T4" s="11" t="n">
+      <c r="T4" s="15" t="n">
         <v>3.44</v>
       </c>
-      <c r="U4" s="12" t="n">
+      <c r="U4" s="16" t="n">
         <v>1.36</v>
       </c>
-      <c r="V4" s="12" t="n">
+      <c r="V4" s="16" t="n">
         <v>2.58</v>
       </c>
-      <c r="W4" s="12" t="n">
+      <c r="W4" s="16" t="n">
         <v>2.08</v>
       </c>
-      <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="6" t="n">
+      <c r="X4" s="8" t="inlineStr"/>
+      <c r="Y4" s="13" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="Z4" s="8" t="inlineStr">
+        <is>
+          <t>12位/19</t>
+        </is>
+      </c>
+      <c r="AA4" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB4" s="10" t="n">
         <v>60000</v>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AC4" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA4" s="14" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 なし(健全)）</t>
+      <c r="AD4" s="5" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 なし(健全)） ／ 【LP】CVR 2.94%＝自店12位/19。中央値以上なのでLPは触らない</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>ナノガラス脱毛パッド</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="21" t="n">
         <v>983060</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="21" t="n">
         <v>185551</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="21" t="n">
         <v>392186</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="21" t="n">
         <v>405323</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="22" t="n">
         <v>0.4123</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="22" t="n">
         <v>0.1887</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="H5" s="22" t="n">
         <v>0.3989</v>
       </c>
-      <c r="I5" s="16" t="n">
+      <c r="I5" s="21" t="n">
         <v>477600</v>
       </c>
-      <c r="J5" s="16" t="n">
+      <c r="J5" s="21" t="n">
         <v>90075</v>
       </c>
-      <c r="K5" s="16" t="n">
+      <c r="K5" s="21" t="n">
         <v>186394</v>
       </c>
-      <c r="L5" s="16" t="n">
+      <c r="L5" s="21" t="n">
         <v>201131</v>
       </c>
-      <c r="M5" s="17" t="n">
+      <c r="M5" s="22" t="n">
         <v>0.4211</v>
       </c>
-      <c r="N5" s="16" t="n">
+      <c r="N5" s="21" t="n">
         <v>206960</v>
       </c>
-      <c r="O5" s="16" t="n">
+      <c r="O5" s="21" t="n">
         <v>39024</v>
       </c>
-      <c r="P5" s="16" t="n">
+      <c r="P5" s="21" t="n">
         <v>66767</v>
       </c>
-      <c r="Q5" s="16" t="n">
+      <c r="Q5" s="21" t="n">
         <v>101169</v>
       </c>
-      <c r="R5" s="17" t="n">
+      <c r="R5" s="22" t="n">
         <v>0.4888</v>
       </c>
-      <c r="S5" s="16" t="n">
+      <c r="S5" s="21" t="n">
         <v>2215841</v>
       </c>
-      <c r="T5" s="11" t="n">
+      <c r="T5" s="15" t="n">
         <v>2.51</v>
       </c>
-      <c r="U5" s="18" t="n">
+      <c r="U5" s="23" t="n">
         <v>1.23</v>
       </c>
-      <c r="V5" s="18" t="n">
+      <c r="V5" s="23" t="n">
         <v>2.17</v>
       </c>
-      <c r="W5" s="18" t="n">
+      <c r="W5" s="23" t="n">
         <v>1.28</v>
       </c>
-      <c r="X5" s="15" t="inlineStr"/>
-      <c r="Y5" s="16" t="n">
+      <c r="X5" s="20" t="inlineStr"/>
+      <c r="Y5" s="18" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="Z5" s="20" t="inlineStr">
+        <is>
+          <t>7位/19</t>
+        </is>
+      </c>
+      <c r="AA5" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB5" s="21" t="n">
         <v>68000</v>
       </c>
-      <c r="Z5" s="15" t="inlineStr">
+      <c r="AC5" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA5" s="19" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 7/30） ／ 【増分MER実測】週次+2.80（週次のみ。直近1段のP1/P2は測定条件を満たさず＝参考値）</t>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 7/30） ／ 【LP】CVR 3.47%＝自店7位/19。中央値以上なのでLPは触らない ／ 【増分MER実測】週次+2.80（週次のみ。直近1段のP1/P2は測定条件を満たさず＝参考値）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>卓上冷感クーラー</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="10" t="n">
         <v>789360</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="10" t="n">
         <v>263472</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="10" t="n">
         <v>211681</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="10" t="n">
         <v>314207</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="11" t="n">
         <v>0.3981</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.3338</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="11" t="n">
         <v>0.2682</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="10" t="n">
         <v>287040</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="10" t="n">
         <v>95808</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="10" t="n">
         <v>106074</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" s="10" t="n">
         <v>85158</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="14" t="n">
         <v>0.2967</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="10" t="n">
         <v>107640</v>
       </c>
-      <c r="O6" s="6" t="n">
+      <c r="O6" s="10" t="n">
         <v>35928</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="P6" s="10" t="n">
         <v>39087</v>
       </c>
-      <c r="Q6" s="6" t="n">
+      <c r="Q6" s="10" t="n">
         <v>32625</v>
       </c>
-      <c r="R6" s="7" t="n">
+      <c r="R6" s="11" t="n">
         <v>0.3031</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="S6" s="10" t="n">
         <v>504903</v>
       </c>
-      <c r="T6" s="11" t="n">
+      <c r="T6" s="15" t="n">
         <v>3.73</v>
       </c>
-      <c r="U6" s="12" t="n">
+      <c r="U6" s="16" t="n">
         <v>1.5</v>
       </c>
-      <c r="V6" s="12" t="n">
+      <c r="V6" s="16" t="n">
         <v>3.16</v>
       </c>
-      <c r="W6" s="12" t="n">
+      <c r="W6" s="16" t="n">
         <v>2.23</v>
       </c>
-      <c r="X6" s="13" t="n">
+      <c r="X6" s="17" t="n">
         <v>-9.539999999999999</v>
       </c>
-      <c r="Y6" s="6" t="n">
+      <c r="Y6" s="13" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="Z6" s="8" t="inlineStr">
+        <is>
+          <t>18位/19</t>
+        </is>
+      </c>
+      <c r="AA6" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB6" s="10" t="n">
         <v>38000</v>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AC6" s="8" t="inlineStr">
         <is>
           <t>🚨 元の予算に戻す</t>
         </is>
       </c>
-      <c r="AA6" s="14" t="inlineStr">
-        <is>
-          <t>【広告】38,000→30,000円/日 ／ 【診断】D1素材疲弊（CTR 4.53%→3.43% (-24%)） ／ 【原価】原価率33.4%&gt;33%。CJに数量交渉／【価格】+1,000円で数量−20.1%まで許容 ／ 【増分MER実測】週次+3.29 / 曜日-9.57 / 全店-9.50（曜日・全店の2手法が一致→採用）</t>
+      <c r="AD6" s="5" t="inlineStr">
+        <is>
+          <t>【広告】38,000→30,000円/日 ／ 【診断】D1a 配信面の拡大（予算増が原因・CRでは直らない）（CTR 4.53%→3.43% (-24%) / インプ+127%・頻度+1%・CPM-14%） ／ 【LP】CVR 1.93%＝自店18位/19（中央値3.18%）→ 商品ページに改善余地あり ／ 【価格】原価率33.4%&gt;33%。残シーズン5週なので原価交渉は間に合わない→値上げのみ。+1,000円で数量−20.1%まで許容 ／ 【増分MER実測】週次+3.29 / 曜日-9.57 / 全店-9.50（曜日・全店の2手法が一致→採用）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>完全遮光・形状記憶・晴雨兼用・UV日傘</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="21" t="n">
         <v>692220</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="21" t="n">
         <v>179333</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="21" t="n">
         <v>271650</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="21" t="n">
         <v>241237</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="22" t="n">
         <v>0.3485</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="22" t="n">
         <v>0.2591</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="H7" s="22" t="n">
         <v>0.3924</v>
       </c>
-      <c r="I7" s="16" t="n">
+      <c r="I7" s="21" t="n">
         <v>224100</v>
       </c>
-      <c r="J7" s="16" t="n">
+      <c r="J7" s="21" t="n">
         <v>57596</v>
       </c>
-      <c r="K7" s="16" t="n">
+      <c r="K7" s="21" t="n">
         <v>121629</v>
       </c>
-      <c r="L7" s="16" t="n">
+      <c r="L7" s="21" t="n">
         <v>44875</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="14" t="n">
         <v>0.2002</v>
       </c>
-      <c r="N7" s="16" t="n">
+      <c r="N7" s="21" t="n">
         <v>74700</v>
       </c>
-      <c r="O7" s="16" t="n">
+      <c r="O7" s="21" t="n">
         <v>19635</v>
       </c>
-      <c r="P7" s="16" t="n">
+      <c r="P7" s="21" t="n">
         <v>44112</v>
       </c>
-      <c r="Q7" s="16" t="n">
+      <c r="Q7" s="21" t="n">
         <v>10953</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="R7" s="14" t="n">
         <v>0.1466</v>
       </c>
-      <c r="S7" s="16" t="n">
+      <c r="S7" s="21" t="n">
         <v>903614</v>
       </c>
-      <c r="T7" s="13" t="n">
+      <c r="T7" s="17" t="n">
         <v>2.55</v>
       </c>
-      <c r="U7" s="18" t="n">
+      <c r="U7" s="23" t="n">
         <v>1.35</v>
       </c>
-      <c r="V7" s="18" t="n">
+      <c r="V7" s="23" t="n">
         <v>2.56</v>
       </c>
-      <c r="W7" s="18" t="n">
+      <c r="W7" s="23" t="n">
         <v>1.2</v>
       </c>
-      <c r="X7" s="13" t="n">
+      <c r="X7" s="17" t="n">
         <v>-7.92</v>
       </c>
-      <c r="Y7" s="16" t="n">
+      <c r="Y7" s="13" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="Z7" s="20" t="inlineStr">
+        <is>
+          <t>11位/19</t>
+        </is>
+      </c>
+      <c r="AA7" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB7" s="21" t="n">
         <v>41000</v>
       </c>
-      <c r="Z7" s="15" t="inlineStr">
+      <c r="AC7" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA7" s="19" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 7/28） ／ 【診断】D3 LP/オファー（CVR 3.7%→2.9% (-20%)） ／ 【LP】FV・レビュー・配送日数を見直し。優先配送の訴求位置も ／ 【増分MER実測】週次+1.11 / 曜日-9.18 / 全店-6.67（曜日・全店の2手法が一致→採用）</t>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 7/28） ／ 【診断】D3 LP/オファー（CVR 3.7%→2.9% (-20%)） ／ 【LP】CVR 2.94%＝自店11位/19。中央値以上なのでLPは触らない ／ 【増分MER実測】週次+1.11 / 曜日-9.18 / 全店-6.67（曜日・全店の2手法が一致→採用）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>接触冷感UVパーカー</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="10" t="n">
         <v>660680</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="10" t="n">
         <v>238044</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="10" t="n">
         <v>221405</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="10" t="n">
         <v>201231</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="11" t="n">
         <v>0.3046</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.3603</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="11" t="n">
         <v>0.3351</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="10" t="n">
         <v>322380</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="10" t="n">
         <v>116154</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="10" t="n">
         <v>102074</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="L8" s="10" t="n">
         <v>104152</v>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="11" t="n">
         <v>0.3231</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="N8" s="10" t="n">
         <v>107460</v>
       </c>
-      <c r="O8" s="6" t="n">
+      <c r="O8" s="10" t="n">
         <v>38718</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="P8" s="10" t="n">
         <v>35244</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="Q8" s="10" t="n">
         <v>33498</v>
       </c>
-      <c r="R8" s="7" t="n">
+      <c r="R8" s="11" t="n">
         <v>0.3117</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="S8" s="10" t="n">
         <v>784868</v>
       </c>
-      <c r="T8" s="13" t="n">
+      <c r="T8" s="17" t="n">
         <v>2.98</v>
       </c>
-      <c r="U8" s="12" t="n">
+      <c r="U8" s="16" t="n">
         <v>1.56</v>
       </c>
-      <c r="V8" s="12" t="n">
+      <c r="V8" s="16" t="n">
         <v>3.45</v>
       </c>
-      <c r="W8" s="12" t="n">
+      <c r="W8" s="16" t="n">
         <v>1.42</v>
       </c>
-      <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="6" t="n">
+      <c r="X8" s="8" t="inlineStr"/>
+      <c r="Y8" s="18" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="Z8" s="8" t="inlineStr">
+        <is>
+          <t>3位/19</t>
+        </is>
+      </c>
+      <c r="AA8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB8" s="10" t="n">
         <v>34000</v>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="AC8" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA8" s="14" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 7/28） ／ 【診断】D4 CPM上昇（CPM 2,545→2,974 (+17%)） ／ 【配信】Advantage+全開放と配信面の偏りを確認 ／ 【原価】原価率36.0%&gt;33%。CJに数量交渉／【価格】+1,000円で数量−28.2%まで許容 ／ 【増分MER実測】週次+4.34 / 曜日+1.11 / 全店+4.37（曜日補正と全店補正で結論が割れる→判定保留）</t>
+      <c r="AD8" s="5" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 7/28） ／ 【診断】D4 CPM上昇（CPM 2,545→2,974 (+17%)） ／ 【LP】CVR 4.21%＝自店3位/19。中央値以上なのでLPは触らない ／ 【配信】Advantage+全開放と配信面の偏りを確認 ／ 【価格】原価率36.0%&gt;33%。残シーズン6週なので原価交渉は間に合わない→値上げのみ。+1,000円で数量−28.2%まで許容 ／ 【増分MER実測】週次+4.34 / 曜日+1.11 / 全店+4.37（曜日補正と全店補正で結論が割れる→判定保留）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>5WAY腰掛けファン</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="21" t="n">
         <v>403380</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="21" t="n">
         <v>149688</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="21" t="n">
         <v>87830</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="21" t="n">
         <v>165862</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="22" t="n">
         <v>0.4112</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="13" t="n">
         <v>0.3711</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="22" t="n">
         <v>0.2177</v>
       </c>
-      <c r="I9" s="16" t="n">
+      <c r="I9" s="21" t="n">
         <v>129480</v>
       </c>
-      <c r="J9" s="16" t="n">
+      <c r="J9" s="21" t="n">
         <v>48048</v>
       </c>
-      <c r="K9" s="16" t="n">
+      <c r="K9" s="21" t="n">
         <v>38325</v>
       </c>
-      <c r="L9" s="16" t="n">
+      <c r="L9" s="21" t="n">
         <v>43107</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="22" t="n">
         <v>0.3329</v>
       </c>
-      <c r="N9" s="16" t="n">
+      <c r="N9" s="21" t="n">
         <v>29880</v>
       </c>
-      <c r="O9" s="16" t="n">
+      <c r="O9" s="21" t="n">
         <v>11088</v>
       </c>
-      <c r="P9" s="16" t="n">
+      <c r="P9" s="21" t="n">
         <v>14444</v>
       </c>
-      <c r="Q9" s="16" t="n">
+      <c r="Q9" s="21" t="n">
         <v>4348</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="R9" s="14" t="n">
         <v>0.1455</v>
       </c>
-      <c r="S9" s="16" t="n">
+      <c r="S9" s="21" t="n">
         <v>175327</v>
       </c>
-      <c r="T9" s="11" t="n">
+      <c r="T9" s="15" t="n">
         <v>4.59</v>
       </c>
-      <c r="U9" s="18" t="n">
+      <c r="U9" s="23" t="n">
         <v>1.59</v>
       </c>
-      <c r="V9" s="18" t="n">
+      <c r="V9" s="23" t="n">
         <v>3.59</v>
       </c>
-      <c r="W9" s="18" t="n">
+      <c r="W9" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="X9" s="15" t="inlineStr"/>
-      <c r="Y9" s="16" t="n">
+      <c r="X9" s="20" t="inlineStr"/>
+      <c r="Y9" s="18" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="Z9" s="20" t="inlineStr">
+        <is>
+          <t>4位/19</t>
+        </is>
+      </c>
+      <c r="AA9" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="21" t="n">
         <v>13000</v>
       </c>
-      <c r="Z9" s="15" t="inlineStr">
+      <c r="AC9" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA9" s="19" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 7/28） ／ 【原価】原価率37.1%&gt;33%。CJに数量交渉／【価格】+1,000円で数量−24.2%まで許容 ／ 【増分MER実測】週次+4.52（週次のみ。直近1段のP1/P2は測定条件を満たさず＝参考値）</t>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 7/28） ／ 【LP】CVR 3.54%＝自店4位/19。中央値以上なのでLPは触らない ／ 【価格】原価率37.1%&gt;33%。残シーズン5週なので原価交渉は間に合わない→値上げのみ。+1,000円で数量−24.2%まで許容 ／ 【増分MER実測】週次+4.52（週次のみ。直近1段のP1/P2は測定条件を満たさず＝参考値）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>3WAYサーキュレーター扇風機</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="10" t="n">
         <v>310960</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="10" t="n">
         <v>129220</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="10" t="n">
         <v>104645</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="10" t="n">
         <v>77095</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="14" t="n">
         <v>0.2479</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.4156</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="11" t="n">
         <v>0.3365</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="10" t="n">
         <v>95680</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="10" t="n">
         <v>39760</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="10" t="n">
         <v>48466</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="L10" s="10" t="n">
         <v>7454</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="14" t="n">
         <v>0.0779</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="N10" s="10" t="n">
         <v>65780</v>
       </c>
-      <c r="O10" s="6" t="n">
+      <c r="O10" s="10" t="n">
         <v>27335</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="P10" s="10" t="n">
         <v>16278</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="Q10" s="10" t="n">
         <v>22167</v>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="R10" s="11" t="n">
         <v>0.337</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="S10" s="10" t="n">
         <v>242250</v>
       </c>
-      <c r="T10" s="13" t="n">
+      <c r="T10" s="17" t="n">
         <v>2.97</v>
       </c>
-      <c r="U10" s="12" t="n">
+      <c r="U10" s="16" t="n">
         <v>1.71</v>
       </c>
-      <c r="V10" s="12" t="n">
+      <c r="V10" s="16" t="n">
         <v>4.27</v>
       </c>
-      <c r="W10" s="12" t="n">
+      <c r="W10" s="16" t="n">
         <v>1.26</v>
       </c>
-      <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="6" t="n">
+      <c r="X10" s="8" t="inlineStr"/>
+      <c r="Y10" s="13" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Z10" s="8" t="inlineStr">
+        <is>
+          <t>15位/19</t>
+        </is>
+      </c>
+      <c r="AA10" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="10" t="n">
         <v>16000</v>
       </c>
-      <c r="Z10" s="4" t="inlineStr">
+      <c r="AC10" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA10" s="14" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 7/29） ／ 【診断】D5需要減衰（CTR/CVR/CPM横ばいでCPAのみ +22%） ／ 【原価】原価率41.6%&gt;33%。CJに数量交渉／【価格】+1,000円で数量−22.2%まで許容 ／ 【増分MER実測】週次+0.59（週次のみ。直近1段のP1/P2は測定条件を満たさず＝参考値）</t>
+      <c r="AD10" s="5" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 7/29） ／ 【診断】D5需要減衰（CTR/CVR/CPM横ばいでCPAのみ +22%） ／ 【LP】CVR 2.75%＝自店15位/19（中央値3.18%）→ 商品ページに改善余地あり ／ 【価格】原価率41.6%&gt;33%。残シーズン5週なので原価交渉は間に合わない→値上げのみ。+1,000円で数量−22.2%まで許容 ／ 【増分MER実測】週次+0.59（週次のみ。直近1段のP1/P2は測定条件を満たさず＝参考値）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>偏光・調光サングラス</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="21" t="n">
         <v>282580</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="21" t="n">
         <v>63403</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="21" t="n">
         <v>153706</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="21" t="n">
         <v>65471</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="14" t="n">
         <v>0.2317</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="22" t="n">
         <v>0.2244</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.5439000000000001</v>
       </c>
-      <c r="I11" s="16" t="n">
+      <c r="I11" s="21" t="n">
         <v>115420</v>
       </c>
-      <c r="J11" s="16" t="n">
+      <c r="J11" s="21" t="n">
         <v>25897</v>
       </c>
-      <c r="K11" s="16" t="n">
+      <c r="K11" s="21" t="n">
         <v>63609</v>
       </c>
-      <c r="L11" s="16" t="n">
+      <c r="L11" s="21" t="n">
         <v>25914</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M11" s="14" t="n">
         <v>0.2245</v>
       </c>
-      <c r="N11" s="16" t="n">
+      <c r="N11" s="21" t="n">
         <v>51740</v>
       </c>
-      <c r="O11" s="16" t="n">
+      <c r="O11" s="21" t="n">
         <v>11609</v>
       </c>
-      <c r="P11" s="16" t="n">
+      <c r="P11" s="21" t="n">
         <v>23803</v>
       </c>
-      <c r="Q11" s="16" t="n">
+      <c r="Q11" s="21" t="n">
         <v>16328</v>
       </c>
-      <c r="R11" s="17" t="n">
+      <c r="R11" s="22" t="n">
         <v>0.3156</v>
       </c>
-      <c r="S11" s="16" t="n">
+      <c r="S11" s="21" t="n">
         <v>568533</v>
       </c>
-      <c r="T11" s="13" t="n">
+      <c r="T11" s="17" t="n">
         <v>1.84</v>
       </c>
-      <c r="U11" s="18" t="n">
+      <c r="U11" s="23" t="n">
         <v>1.29</v>
       </c>
-      <c r="V11" s="18" t="n">
+      <c r="V11" s="23" t="n">
         <v>2.35</v>
       </c>
-      <c r="W11" s="18" t="n">
+      <c r="W11" s="23" t="n">
         <v>0.55</v>
       </c>
-      <c r="X11" s="15" t="inlineStr"/>
-      <c r="Y11" s="16" t="n">
+      <c r="X11" s="20" t="inlineStr"/>
+      <c r="Y11" s="13" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="Z11" s="20" t="inlineStr">
+        <is>
+          <t>14位/19</t>
+        </is>
+      </c>
+      <c r="AA11" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB11" s="21" t="n">
         <v>22000</v>
       </c>
-      <c r="Z11" s="15" t="inlineStr">
+      <c r="AC11" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA11" s="19" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 7/29） ／ 【診断】D3 LP/オファー（CVR 3.4%→2.8% (-17%)） ／ 【LP】FV・レビュー・配送日数を見直し。優先配送の訴求位置も ／ 【広告費率】40%超。CR・LPで手当て（率のために黒字を削らない）</t>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 7/29） ／ 【診断】D3 LP/オファー（CVR 3.4%→2.8% (-17%)） ／ 【LP】CVR 2.78%＝自店14位/19。中央値以上なのでLPは触らない ／ 【広告費率】40%超（率のために黒字は削らない）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>ムダ毛シェーバー</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="10" t="n">
         <v>269100</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="10" t="n">
         <v>125910</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="10" t="n">
         <v>93605</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="10" t="n">
         <v>49585</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="14" t="n">
         <v>0.1843</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.4679</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="11" t="n">
         <v>0.3478</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="10" t="n">
         <v>125580</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="10" t="n">
         <v>58758</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="10" t="n">
         <v>39050</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="L12" s="10" t="n">
         <v>27772</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M12" s="14" t="n">
         <v>0.2211</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" s="10" t="n">
         <v>59800</v>
       </c>
-      <c r="O12" s="6" t="n">
+      <c r="O12" s="10" t="n">
         <v>27980</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="P12" s="10" t="n">
         <v>16309</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="Q12" s="10" t="n">
         <v>15511</v>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="R12" s="14" t="n">
         <v>0.2594</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="S12" s="10" t="n">
         <v>71270</v>
       </c>
-      <c r="T12" s="13" t="n">
+      <c r="T12" s="17" t="n">
         <v>2.87</v>
       </c>
-      <c r="U12" s="12" t="n">
+      <c r="U12" s="16" t="n">
         <v>1.88</v>
       </c>
-      <c r="V12" s="12" t="n">
+      <c r="V12" s="16" t="n">
         <v>5.49</v>
       </c>
-      <c r="W12" s="12" t="n">
+      <c r="W12" s="16" t="n">
         <v>0.99</v>
       </c>
-      <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="6" t="n">
+      <c r="X12" s="8" t="inlineStr"/>
+      <c r="Y12" s="18" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="Z12" s="8" t="inlineStr">
+        <is>
+          <t>6位/19</t>
+        </is>
+      </c>
+      <c r="AA12" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB12" s="10" t="n">
         <v>13000</v>
       </c>
-      <c r="Z12" s="4" t="inlineStr">
+      <c r="AC12" s="8" t="inlineStr">
         <is>
           <t>✅ 維持（CR/LP/価格で手当て）</t>
         </is>
       </c>
-      <c r="AA12" s="14" t="inlineStr">
-        <is>
-          <t>【広告】13,000円/日 据置 ／ 【原価】原価率46.8%&gt;33%。CJに数量交渉／【価格】+1,000円で数量−23.9%まで許容</t>
+      <c r="AD12" s="5" t="inlineStr">
+        <is>
+          <t>【広告】13,000円/日 据置 ／ 【LP】CVR 3.51%＝自店6位/19。中央値以上なのでLPは触らない ／ 【原価】原価率46.8%&gt;33%。通年商品なのでCJ数量交渉が有効／【価格】+1,000円で数量−23.9%まで許容</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>接触冷感UVアームカバー</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="21" t="n">
         <v>250740</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="21" t="n">
         <v>49392</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="21" t="n">
         <v>120456</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="21" t="n">
         <v>80892</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="22" t="n">
         <v>0.3226</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="22" t="n">
         <v>0.197</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.4804</v>
       </c>
-      <c r="I13" s="16" t="n">
+      <c r="I13" s="21" t="n">
         <v>123380</v>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="21" t="n">
         <v>24304</v>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="21" t="n">
         <v>52425</v>
       </c>
-      <c r="L13" s="16" t="n">
+      <c r="L13" s="21" t="n">
         <v>46651</v>
       </c>
-      <c r="M13" s="17" t="n">
+      <c r="M13" s="22" t="n">
         <v>0.3781</v>
       </c>
-      <c r="N13" s="16" t="n">
+      <c r="N13" s="21" t="n">
         <v>43780</v>
       </c>
-      <c r="O13" s="16" t="n">
+      <c r="O13" s="21" t="n">
         <v>8624</v>
       </c>
-      <c r="P13" s="16" t="n">
+      <c r="P13" s="21" t="n">
         <v>19102</v>
       </c>
-      <c r="Q13" s="16" t="n">
+      <c r="Q13" s="21" t="n">
         <v>16054</v>
       </c>
-      <c r="R13" s="17" t="n">
+      <c r="R13" s="22" t="n">
         <v>0.3667</v>
       </c>
-      <c r="S13" s="16" t="n">
+      <c r="S13" s="21" t="n">
         <v>409022</v>
       </c>
-      <c r="T13" s="13" t="n">
+      <c r="T13" s="17" t="n">
         <v>2.08</v>
       </c>
-      <c r="U13" s="18" t="n">
+      <c r="U13" s="23" t="n">
         <v>1.25</v>
       </c>
-      <c r="V13" s="18" t="n">
+      <c r="V13" s="23" t="n">
         <v>2.21</v>
       </c>
-      <c r="W13" s="18" t="n">
+      <c r="W13" s="23" t="n">
         <v>0.83</v>
       </c>
-      <c r="X13" s="15" t="inlineStr"/>
-      <c r="Y13" s="16" t="n">
+      <c r="X13" s="20" t="inlineStr"/>
+      <c r="Y13" s="18" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="Z13" s="20" t="inlineStr">
+        <is>
+          <t>2位/19</t>
+        </is>
+      </c>
+      <c r="AA13" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB13" s="21" t="n">
         <v>17000</v>
       </c>
-      <c r="Z13" s="15" t="inlineStr">
+      <c r="AC13" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA13" s="19" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 7/29） ／ 【診断】D1素材疲弊（CTR 2.59%→2.18% (-16%)） ／ 【広告費率】40%超。CR・LPで手当て（率のために黒字を削らない）</t>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 7/29） ／ 【診断】D1素材疲弊（CTR 2.59%→2.18% (-16%)） ／ 【LP】CVR 4.68%＝自店2位/19。中央値以上なのでLPは触らない ／ 【広告費率】40%超（率のために黒字は削らない）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>瞬間冷感ポンチョ</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="10" t="n">
         <v>202980</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="10" t="n">
         <v>50337</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="10" t="n">
         <v>92790</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="10" t="n">
         <v>59853</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="14" t="n">
         <v>0.2949</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="11" t="n">
         <v>0.248</v>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.4571</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="10" t="n">
         <v>99500</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="10" t="n">
         <v>24675</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" s="10" t="n">
         <v>38189</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="10" t="n">
         <v>36636</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="11" t="n">
         <v>0.3682</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="N14" s="10" t="n">
         <v>23880</v>
       </c>
-      <c r="O14" s="6" t="n">
+      <c r="O14" s="10" t="n">
         <v>5922</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="P14" s="10" t="n">
         <v>13423</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q14" s="10" t="n">
         <v>4535</v>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="R14" s="14" t="n">
         <v>0.1899</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="S14" s="10" t="n">
         <v>137618</v>
       </c>
-      <c r="T14" s="13" t="n">
+      <c r="T14" s="17" t="n">
         <v>2.19</v>
       </c>
-      <c r="U14" s="12" t="n">
+      <c r="U14" s="16" t="n">
         <v>1.33</v>
       </c>
-      <c r="V14" s="12" t="n">
+      <c r="V14" s="16" t="n">
         <v>2.49</v>
       </c>
-      <c r="W14" s="12" t="n">
+      <c r="W14" s="16" t="n">
         <v>0.86</v>
       </c>
-      <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="6" t="n">
+      <c r="X14" s="8" t="inlineStr"/>
+      <c r="Y14" s="13" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
+        <is>
+          <t>13位/19</t>
+        </is>
+      </c>
+      <c r="AA14" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB14" s="10" t="n">
         <v>13000</v>
       </c>
-      <c r="Z14" s="4" t="inlineStr">
+      <c r="AC14" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA14" s="14" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 8/1） ／ 【広告費率】40%超。CR・LPで手当て（率のために黒字を削らない）</t>
+      <c r="AD14" s="5" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 8/1） ／ 【LP】CVR 2.80%＝自店13位/19。中央値以上なのでLPは触らない ／ 【広告費率】40%超（率のために黒字は削らない）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>健康サンダル</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="21" t="n">
         <v>194220</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="21" t="n">
         <v>42994</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="21" t="n">
         <v>92591</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="21" t="n">
         <v>58635</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="22" t="n">
         <v>0.3019</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="22" t="n">
         <v>0.2214</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.4767</v>
       </c>
-      <c r="I15" s="16" t="n">
+      <c r="I15" s="21" t="n">
         <v>69720</v>
       </c>
-      <c r="J15" s="16" t="n">
+      <c r="J15" s="21" t="n">
         <v>16268</v>
       </c>
-      <c r="K15" s="16" t="n">
+      <c r="K15" s="21" t="n">
         <v>40922</v>
       </c>
-      <c r="L15" s="16" t="n">
+      <c r="L15" s="21" t="n">
         <v>12530</v>
       </c>
-      <c r="M15" s="10" t="n">
+      <c r="M15" s="14" t="n">
         <v>0.1797</v>
       </c>
-      <c r="N15" s="16" t="n">
+      <c r="N15" s="21" t="n">
         <v>24900</v>
       </c>
-      <c r="O15" s="16" t="n">
+      <c r="O15" s="21" t="n">
         <v>5810</v>
       </c>
-      <c r="P15" s="16" t="n">
+      <c r="P15" s="21" t="n">
         <v>14273</v>
       </c>
-      <c r="Q15" s="16" t="n">
+      <c r="Q15" s="21" t="n">
         <v>4817</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="R15" s="14" t="n">
         <v>0.1935</v>
       </c>
-      <c r="S15" s="16" t="n">
+      <c r="S15" s="21" t="n">
         <v>307384</v>
       </c>
-      <c r="T15" s="13" t="n">
+      <c r="T15" s="17" t="n">
         <v>2.1</v>
       </c>
-      <c r="U15" s="18" t="n">
+      <c r="U15" s="23" t="n">
         <v>1.28</v>
       </c>
-      <c r="V15" s="18" t="n">
+      <c r="V15" s="23" t="n">
         <v>2.33</v>
       </c>
-      <c r="W15" s="18" t="n">
+      <c r="W15" s="23" t="n">
         <v>0.82</v>
       </c>
-      <c r="X15" s="15" t="inlineStr"/>
-      <c r="Y15" s="16" t="n">
+      <c r="X15" s="20" t="inlineStr"/>
+      <c r="Y15" s="18" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="Z15" s="20" t="inlineStr">
+        <is>
+          <t>8位/19</t>
+        </is>
+      </c>
+      <c r="AA15" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB15" s="21" t="n">
         <v>13000</v>
       </c>
-      <c r="Z15" s="15" t="inlineStr">
+      <c r="AC15" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA15" s="19" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 なし(健全)） ／ 【広告費率】40%超。CR・LPで手当て（率のために黒字を削らない）</t>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 なし(健全)） ／ 【LP】CVR 3.39%＝自店8位/19。中央値以上なのでLPは触らない ／ 【広告費率】40%超（率のために黒字は削らない）</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>UV歯ブラシ除菌器</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="10" t="n">
         <v>161640</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="10" t="n">
         <v>58320</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="10" t="n">
         <v>76804</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="10" t="n">
         <v>26516</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="14" t="n">
         <v>0.164</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="13" t="n">
         <v>0.3608</v>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.4752</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="10" t="n">
         <v>107760</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="10" t="n">
         <v>38880</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="K16" s="10" t="n">
         <v>28271</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="10" t="n">
         <v>40609</v>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="11" t="n">
         <v>0.3768</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" s="10" t="n">
         <v>35920</v>
       </c>
-      <c r="O16" s="6" t="n">
+      <c r="O16" s="10" t="n">
         <v>12960</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="P16" s="10" t="n">
         <v>10280</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="Q16" s="10" t="n">
         <v>12680</v>
       </c>
-      <c r="R16" s="7" t="n">
+      <c r="R16" s="11" t="n">
         <v>0.353</v>
       </c>
-      <c r="S16" s="6" t="n">
+      <c r="S16" s="10" t="n">
         <v>238262</v>
       </c>
-      <c r="T16" s="13" t="n">
+      <c r="T16" s="17" t="n">
         <v>2.1</v>
       </c>
-      <c r="U16" s="12" t="n">
+      <c r="U16" s="16" t="n">
         <v>1.56</v>
       </c>
-      <c r="V16" s="12" t="n">
+      <c r="V16" s="16" t="n">
         <v>3.46</v>
       </c>
-      <c r="W16" s="12" t="n">
+      <c r="W16" s="16" t="n">
         <v>0.54</v>
       </c>
-      <c r="X16" s="4" t="inlineStr"/>
-      <c r="Y16" s="6" t="n">
+      <c r="X16" s="8" t="inlineStr"/>
+      <c r="Y16" s="13" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
+        <is>
+          <t>16位/19</t>
+        </is>
+      </c>
+      <c r="AA16" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB16" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="Z16" s="4" t="inlineStr">
+      <c r="AC16" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA16" s="14" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 7/30） ／ 【診断】D3 LP/オファー（CVR 3.6%→2.6% (-28%)） ／ 【LP】FV・レビュー・配送日数を見直し。優先配送の訴求位置も ／ 【原価】原価率36.1%&gt;33%。CJに数量交渉／【価格】+1,000円で数量−14.8%まで許容 ／ 【広告費率】40%超。CR・LPで手当て（率のために黒字を削らない）</t>
+      <c r="AD16" s="5" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 7/30） ／ 【診断】D3 LP/オファー（CVR 3.6%→2.6% (-28%)） ／ 【LP】CVR 2.60%＝自店16位/19（中央値3.18%）→ 商品ページに改善余地あり ／ 【原価】原価率36.1%&gt;33%。通年商品なのでCJ数量交渉が有効／【価格】+1,000円で数量−14.8%まで許容 ／ 【広告費率】40%超（率のために黒字は削らない）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>携帯電動シェーバー</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="21" t="n">
         <v>139440</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="21" t="n">
         <v>47061</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="21" t="n">
         <v>77741</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="21" t="n">
         <v>14638</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="14" t="n">
         <v>0.105</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="13" t="n">
         <v>0.3375</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.5575</v>
       </c>
-      <c r="I17" s="16" t="n">
+      <c r="I17" s="21" t="n">
         <v>49800</v>
       </c>
-      <c r="J17" s="16" t="n">
+      <c r="J17" s="21" t="n">
         <v>17430</v>
       </c>
-      <c r="K17" s="16" t="n">
+      <c r="K17" s="21" t="n">
         <v>32991</v>
       </c>
-      <c r="L17" s="20" t="n">
+      <c r="L17" s="25" t="n">
         <v>-621</v>
       </c>
-      <c r="M17" s="21" t="n">
+      <c r="M17" s="26" t="n">
         <v>-0.0125</v>
       </c>
-      <c r="N17" s="16" t="n">
+      <c r="N17" s="21" t="n">
         <v>24900</v>
       </c>
-      <c r="O17" s="16" t="n">
+      <c r="O17" s="21" t="n">
         <v>8715</v>
       </c>
-      <c r="P17" s="16" t="n">
+      <c r="P17" s="21" t="n">
         <v>12572</v>
       </c>
-      <c r="Q17" s="16" t="n">
+      <c r="Q17" s="21" t="n">
         <v>3613</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="14" t="n">
         <v>0.1451</v>
       </c>
-      <c r="S17" s="16" t="n">
+      <c r="S17" s="21" t="n">
         <v>214304</v>
       </c>
-      <c r="T17" s="13" t="n">
+      <c r="T17" s="17" t="n">
         <v>1.79</v>
       </c>
-      <c r="U17" s="18" t="n">
+      <c r="U17" s="23" t="n">
         <v>1.51</v>
       </c>
-      <c r="V17" s="18" t="n">
+      <c r="V17" s="23" t="n">
         <v>3.2</v>
       </c>
-      <c r="W17" s="18" t="n">
+      <c r="W17" s="23" t="n">
         <v>0.28</v>
       </c>
-      <c r="X17" s="15" t="inlineStr"/>
-      <c r="Y17" s="16" t="n">
+      <c r="X17" s="20" t="inlineStr"/>
+      <c r="Y17" s="18" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="Z17" s="20" t="inlineStr">
+        <is>
+          <t>10位/19</t>
+        </is>
+      </c>
+      <c r="AA17" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB17" s="21" t="n">
         <v>11000</v>
       </c>
-      <c r="Z17" s="15" t="inlineStr">
+      <c r="AC17" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA17" s="19" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 8/1） ／ 【原価】原価率33.8%&gt;33%。CJに数量交渉／【価格】+1,000円で数量−23.6%まで許容 ／ 【広告費率】40%超。CR・LPで手当て（率のために黒字を削らない）</t>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 8/1） ／ 【LP】CVR 3.18%＝自店10位/19。中央値以上なのでLPは触らない ／ 【原価】原価率33.8%&gt;33%。通年商品なのでCJ数量交渉が有効／【価格】+1,000円で数量−23.6%まで許容 ／ 【広告費率】40%超（率のために黒字は削らない）</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>バランスケアスリッパ</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="10" t="n">
         <v>89640</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="10" t="n">
         <v>23472</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="10" t="n">
         <v>47894</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="10" t="n">
         <v>18274</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="14" t="n">
         <v>0.2039</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="11" t="n">
         <v>0.2618</v>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.5343</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="10" t="n">
         <v>44820</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="10" t="n">
         <v>11736</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="K18" s="10" t="n">
         <v>15025</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="10" t="n">
         <v>18059</v>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="11" t="n">
         <v>0.4029</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="N18" s="10" t="n">
         <v>24900</v>
       </c>
-      <c r="O18" s="6" t="n">
+      <c r="O18" s="10" t="n">
         <v>6520</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="P18" s="10" t="n">
         <v>5678</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q18" s="10" t="n">
         <v>12702</v>
       </c>
-      <c r="R18" s="7" t="n">
+      <c r="R18" s="11" t="n">
         <v>0.5101</v>
       </c>
-      <c r="S18" s="6" t="n">
+      <c r="S18" s="10" t="n">
         <v>89092</v>
       </c>
-      <c r="T18" s="13" t="n">
+      <c r="T18" s="17" t="n">
         <v>1.87</v>
       </c>
-      <c r="U18" s="12" t="n">
+      <c r="U18" s="16" t="n">
         <v>1.35</v>
       </c>
-      <c r="V18" s="12" t="n">
+      <c r="V18" s="16" t="n">
         <v>2.58</v>
       </c>
-      <c r="W18" s="12" t="n">
+      <c r="W18" s="16" t="n">
         <v>0.52</v>
       </c>
-      <c r="X18" s="13" t="n">
+      <c r="X18" s="17" t="n">
         <v>0.91</v>
       </c>
-      <c r="Y18" s="6" t="n">
+      <c r="Y18" s="18" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="Z18" s="8" t="inlineStr">
+        <is>
+          <t>9位/19</t>
+        </is>
+      </c>
+      <c r="AA18" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB18" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="Z18" s="4" t="inlineStr">
+      <c r="AC18" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA18" s="14" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 7/29） ／ 【診断】D3 LP/オファー（CVR 4.6%→3.2% (-31%)） ／ 【LP】FV・レビュー・配送日数を見直し。優先配送の訴求位置も ／ 【広告費率】40%超。CR・LPで手当て（率のために黒字を削らない） ／ 【増分MER実測】週次+1.89 / 曜日+1.09 / 全店+0.73（曜日・全店の2手法が一致→採用）</t>
+      <c r="AD18" s="5" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 7/29） ／ 【診断】D3 LP/オファー（CVR 4.6%→3.2% (-31%)） ／ 【LP】CVR 3.21%＝自店9位/19。中央値以上なのでLPは触らない ／ 【広告費率】40%超（率のために黒字は削らない） ／ 【増分MER実測】週次+1.89 / 曜日+1.09 / 全店+0.73（曜日・全店の2手法が一致→採用）</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>壁掛けディスペンサー</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="21" t="n">
         <v>84740</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="21" t="n">
         <v>24526</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="21" t="n">
         <v>76617</v>
       </c>
-      <c r="E19" s="20" t="n">
+      <c r="E19" s="25" t="n">
         <v>-16403</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="F19" s="26" t="n">
         <v>-0.1936</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="22" t="n">
         <v>0.2894</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.9041</v>
       </c>
-      <c r="I19" s="16" t="n">
+      <c r="I19" s="21" t="n">
         <v>45860</v>
       </c>
-      <c r="J19" s="16" t="n">
+      <c r="J19" s="21" t="n">
         <v>10999</v>
       </c>
-      <c r="K19" s="16" t="n">
+      <c r="K19" s="21" t="n">
         <v>28269</v>
       </c>
-      <c r="L19" s="16" t="n">
+      <c r="L19" s="21" t="n">
         <v>6592</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M19" s="14" t="n">
         <v>0.1437</v>
       </c>
-      <c r="N19" s="16" t="n">
+      <c r="N19" s="21" t="n">
         <v>18940</v>
       </c>
-      <c r="O19" s="16" t="n">
+      <c r="O19" s="21" t="n">
         <v>1434</v>
       </c>
-      <c r="P19" s="16" t="n">
+      <c r="P19" s="21" t="n">
         <v>6427</v>
       </c>
-      <c r="Q19" s="16" t="n">
+      <c r="Q19" s="21" t="n">
         <v>11079</v>
       </c>
-      <c r="R19" s="17" t="n">
+      <c r="R19" s="22" t="n">
         <v>0.585</v>
       </c>
-      <c r="S19" s="16" t="n">
+      <c r="S19" s="21" t="n">
         <v>128591</v>
       </c>
-      <c r="T19" s="13" t="n">
+      <c r="T19" s="17" t="n">
         <v>1.11</v>
       </c>
-      <c r="U19" s="18" t="n">
+      <c r="U19" s="23" t="n">
         <v>1.41</v>
       </c>
-      <c r="V19" s="18" t="n">
+      <c r="V19" s="23" t="n">
         <v>2.77</v>
       </c>
-      <c r="W19" s="18" t="n">
+      <c r="W19" s="23" t="n">
         <v>-0.3</v>
       </c>
-      <c r="X19" s="13" t="n">
+      <c r="X19" s="17" t="n">
         <v>0.36</v>
       </c>
-      <c r="Y19" s="16" t="n">
+      <c r="Y19" s="13" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="Z19" s="20" t="inlineStr">
+        <is>
+          <t>19位/19</t>
+        </is>
+      </c>
+      <c r="AA19" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB19" s="21" t="n">
         <v>6000</v>
       </c>
-      <c r="Z19" s="15" t="inlineStr">
+      <c r="AC19" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="AA19" s="19" t="inlineStr">
-        <is>
-          <t>【広告】据置（次回判定 8/1） ／ 【診断】D3 LP/オファー（CVR 2.0%→1.4% (-30%)） ／ 【LP】FV・レビュー・配送日数を見直し。優先配送の訴求位置も ／ 【広告費率】40%超。CR・LPで手当て（率のために黒字を削らない） ／ 【増分MER実測】週次+3.33 / 曜日+0.50 / 全店+0.22（曜日・全店の2手法が一致→採用）</t>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>【広告】据置（次回判定 8/1） ／ 【診断】D3 LP/オファー（CVR 2.0%→1.4% (-30%)） ／ 【LP】CVR 1.42%＝自店19位/19（中央値3.18%）→ 商品ページに改善余地あり ／ 【広告費率】40%超（率のために黒字は削らない） ／ 【増分MER実測】週次+3.33 / 曜日+0.50 / 全店+0.22（曜日・全店の2手法が一致→採用）</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>湯上がりガーゼワンピース</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="10" t="n">
         <v>71760</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="10" t="n">
         <v>23616</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="10" t="n">
         <v>42068</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="10" t="n">
         <v>6076</v>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="14" t="n">
         <v>0.0847</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="11" t="n">
         <v>0.3291</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.5862000000000001</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="10" t="n">
         <v>17940</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="10" t="n">
         <v>5904</v>
       </c>
-      <c r="K20" s="6" t="n">
+      <c r="K20" s="10" t="n">
         <v>15925</v>
       </c>
-      <c r="L20" s="22" t="n">
+      <c r="L20" s="27" t="n">
         <v>-3889</v>
       </c>
-      <c r="M20" s="21" t="n">
+      <c r="M20" s="26" t="n">
         <v>-0.2168</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="N20" s="10" t="n">
         <v>17940</v>
       </c>
-      <c r="O20" s="6" t="n">
+      <c r="O20" s="10" t="n">
         <v>5904</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="P20" s="10" t="n">
         <v>4254</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="Q20" s="10" t="n">
         <v>7782</v>
       </c>
-      <c r="R20" s="7" t="n">
+      <c r="R20" s="11" t="n">
         <v>0.4338</v>
       </c>
-      <c r="S20" s="6" t="n">
+      <c r="S20" s="10" t="n">
         <v>91106</v>
       </c>
-      <c r="T20" s="13" t="n">
+      <c r="T20" s="17" t="n">
         <v>1.71</v>
       </c>
-      <c r="U20" s="12" t="n">
+      <c r="U20" s="16" t="n">
         <v>1.49</v>
       </c>
-      <c r="V20" s="12" t="n">
+      <c r="V20" s="16" t="n">
         <v>3.12</v>
       </c>
-      <c r="W20" s="12" t="n">
+      <c r="W20" s="16" t="n">
         <v>0.22</v>
       </c>
-      <c r="X20" s="4" t="inlineStr"/>
-      <c r="Y20" s="4" t="inlineStr">
+      <c r="X20" s="8" t="inlineStr"/>
+      <c r="Y20" s="13" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="Z20" s="8" t="inlineStr">
+        <is>
+          <t>17位/19</t>
+        </is>
+      </c>
+      <c r="AA20" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB20" s="8" t="inlineStr">
         <is>
           <t>停止中</t>
         </is>
       </c>
-      <c r="Z20" s="4" t="inlineStr">
+      <c r="AC20" s="8" t="inlineStr">
         <is>
           <t>⏹ 停止済み</t>
         </is>
       </c>
-      <c r="AA20" s="14" t="inlineStr">
+      <c r="AD20" s="5" t="inlineStr">
         <is>
           <t>【広告】7/26に停止済み（0円/日）。再開は8月以降の秋物枠選定とあわせて検討 ／ 停止時点の診断: D3 LP/オファー（CVR 3.0%→2.1%）</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>優先配送</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="21" t="n">
         <v>43952</v>
       </c>
-      <c r="C21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="16" t="n">
+      <c r="C21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="21" t="n">
         <v>43952</v>
       </c>
-      <c r="F21" s="17" t="n">
+      <c r="F21" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="16" t="n">
+      <c r="G21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="21" t="n">
         <v>15544</v>
       </c>
-      <c r="J21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="16" t="n">
+      <c r="J21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="21" t="n">
         <v>15544</v>
       </c>
-      <c r="M21" s="17" t="n">
+      <c r="M21" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="16" t="n">
+      <c r="N21" s="21" t="n">
         <v>5896</v>
       </c>
-      <c r="O21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="16" t="n">
+      <c r="O21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="21" t="n">
         <v>5896</v>
       </c>
-      <c r="R21" s="17" t="n">
+      <c r="R21" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="S21" s="16" t="n">
+      <c r="S21" s="21" t="n">
         <v>116312</v>
       </c>
-      <c r="T21" s="15" t="inlineStr"/>
-      <c r="U21" s="15" t="inlineStr"/>
-      <c r="V21" s="18" t="n">
+      <c r="T21" s="20" t="inlineStr"/>
+      <c r="U21" s="20" t="inlineStr"/>
+      <c r="V21" s="23" t="n">
         <v>1.54</v>
       </c>
-      <c r="W21" s="15" t="inlineStr"/>
-      <c r="X21" s="15" t="inlineStr"/>
-      <c r="Y21" s="15" t="inlineStr">
+      <c r="W21" s="20" t="inlineStr"/>
+      <c r="X21" s="20" t="inlineStr"/>
+      <c r="Y21" s="20" t="inlineStr"/>
+      <c r="Z21" s="20" t="inlineStr"/>
+      <c r="AA21" s="20" t="inlineStr"/>
+      <c r="AB21" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z21" s="15" t="inlineStr">
+      <c r="AC21" s="20" t="inlineStr">
         <is>
           <t>📦広告なし</t>
         </is>
       </c>
-      <c r="AA21" s="19" t="inlineStr">
+      <c r="AD21" s="24" t="inlineStr">
         <is>
           <t>広告費ゼロ。利益=売上−原価</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>瞬間冷却ハンディファン</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="10" t="n">
         <v>29900</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="10" t="n">
         <v>10265</v>
       </c>
-      <c r="D22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6" t="n">
+      <c r="D22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10" t="n">
         <v>19635</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="11" t="n">
         <v>0.6567</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="13" t="n">
         <v>0.3433</v>
       </c>
-      <c r="H22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="6" t="n">
+      <c r="H22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="10" t="n">
         <v>5980</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="10" t="n">
         <v>2053</v>
       </c>
-      <c r="K22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="6" t="n">
+      <c r="K22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="10" t="n">
         <v>3927</v>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="11" t="n">
         <v>0.6567</v>
       </c>
-      <c r="N22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="4" t="inlineStr"/>
-      <c r="S22" s="6" t="n">
+      <c r="N22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8" t="inlineStr"/>
+      <c r="S22" s="10" t="n">
         <v>70686</v>
       </c>
-      <c r="T22" s="4" t="inlineStr"/>
-      <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="12" t="n">
+      <c r="T22" s="8" t="inlineStr"/>
+      <c r="U22" s="8" t="inlineStr"/>
+      <c r="V22" s="16" t="n">
         <v>3.26</v>
       </c>
-      <c r="W22" s="4" t="inlineStr"/>
-      <c r="X22" s="4" t="inlineStr"/>
-      <c r="Y22" s="4" t="inlineStr">
+      <c r="W22" s="8" t="inlineStr"/>
+      <c r="X22" s="8" t="inlineStr"/>
+      <c r="Y22" s="8" t="inlineStr"/>
+      <c r="Z22" s="8" t="inlineStr"/>
+      <c r="AA22" s="8" t="inlineStr"/>
+      <c r="AB22" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z22" s="4" t="inlineStr">
+      <c r="AC22" s="8" t="inlineStr">
         <is>
           <t>📦広告なし</t>
         </is>
       </c>
-      <c r="AA22" s="14" t="inlineStr">
+      <c r="AD22" s="5" t="inlineStr">
         <is>
           <t>広告費ゼロ。利益=売上−原価</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>完全遮光・接触冷感UVハット</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="21" t="n">
         <v>11960</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="21" t="n">
         <v>2822</v>
       </c>
-      <c r="D23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="21" t="n">
         <v>9138</v>
       </c>
-      <c r="F23" s="17" t="n">
+      <c r="F23" s="22" t="n">
         <v>0.764</v>
       </c>
-      <c r="G23" s="17" t="n">
+      <c r="G23" s="22" t="n">
         <v>0.236</v>
       </c>
-      <c r="H23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="15" t="inlineStr"/>
-      <c r="N23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="15" t="inlineStr"/>
-      <c r="S23" s="16" t="n">
+      <c r="H23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="20" t="inlineStr"/>
+      <c r="N23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="20" t="inlineStr"/>
+      <c r="S23" s="21" t="n">
         <v>41121</v>
       </c>
-      <c r="T23" s="15" t="inlineStr"/>
-      <c r="U23" s="15" t="inlineStr"/>
-      <c r="V23" s="18" t="n">
+      <c r="T23" s="20" t="inlineStr"/>
+      <c r="U23" s="20" t="inlineStr"/>
+      <c r="V23" s="23" t="n">
         <v>2.42</v>
       </c>
-      <c r="W23" s="15" t="inlineStr"/>
-      <c r="X23" s="15" t="inlineStr"/>
-      <c r="Y23" s="15" t="inlineStr">
+      <c r="W23" s="20" t="inlineStr"/>
+      <c r="X23" s="20" t="inlineStr"/>
+      <c r="Y23" s="20" t="inlineStr"/>
+      <c r="Z23" s="20" t="inlineStr"/>
+      <c r="AA23" s="20" t="inlineStr"/>
+      <c r="AB23" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z23" s="15" t="inlineStr">
+      <c r="AC23" s="20" t="inlineStr">
         <is>
           <t>📦広告なし</t>
         </is>
       </c>
-      <c r="AA23" s="19" t="inlineStr">
+      <c r="AD23" s="24" t="inlineStr">
         <is>
           <t>広告費ゼロ。利益=売上−原価</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>ネックマッサージャー</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="4" t="inlineStr"/>
-      <c r="S24" s="6" t="n">
+      <c r="B24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="8" t="inlineStr"/>
+      <c r="G24" s="8" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="8" t="inlineStr"/>
+      <c r="S24" s="10" t="n">
         <v>6946</v>
       </c>
-      <c r="T24" s="4" t="inlineStr"/>
-      <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="4" t="inlineStr"/>
-      <c r="W24" s="4" t="inlineStr"/>
-      <c r="X24" s="4" t="inlineStr"/>
-      <c r="Y24" s="4" t="inlineStr">
+      <c r="T24" s="8" t="inlineStr"/>
+      <c r="U24" s="8" t="inlineStr"/>
+      <c r="V24" s="8" t="inlineStr"/>
+      <c r="W24" s="8" t="inlineStr"/>
+      <c r="X24" s="8" t="inlineStr"/>
+      <c r="Y24" s="8" t="inlineStr"/>
+      <c r="Z24" s="8" t="inlineStr"/>
+      <c r="AA24" s="8" t="inlineStr"/>
+      <c r="AB24" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z24" s="4" t="inlineStr">
+      <c r="AC24" s="8" t="inlineStr">
         <is>
           <t>📦広告なし</t>
         </is>
       </c>
-      <c r="AA24" s="14" t="inlineStr">
+      <c r="AD24" s="5" t="inlineStr">
         <is>
           <t>広告費ゼロ。利益=売上−原価</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>ナノバブルシャワーヘッド</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="20" t="inlineStr"/>
+      <c r="I25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="20" t="inlineStr"/>
+      <c r="N25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="20" t="inlineStr"/>
+      <c r="S25" s="21" t="n">
+        <v>51975</v>
+      </c>
+      <c r="T25" s="20" t="inlineStr"/>
+      <c r="U25" s="20" t="inlineStr"/>
+      <c r="V25" s="20" t="inlineStr"/>
+      <c r="W25" s="20" t="inlineStr"/>
+      <c r="X25" s="20" t="inlineStr"/>
+      <c r="Y25" s="20" t="inlineStr"/>
+      <c r="Z25" s="20" t="inlineStr"/>
+      <c r="AA25" s="20" t="inlineStr"/>
+      <c r="AB25" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC25" s="20" t="inlineStr">
+        <is>
+          <t>📦広告なし</t>
+        </is>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>広告費ゼロ。利益=売上−原価</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>リカバリーサンダル</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="8" t="inlineStr"/>
+      <c r="S26" s="10" t="n">
+        <v>18697</v>
+      </c>
+      <c r="T26" s="8" t="inlineStr"/>
+      <c r="U26" s="8" t="inlineStr"/>
+      <c r="V26" s="8" t="inlineStr"/>
+      <c r="W26" s="8" t="inlineStr"/>
+      <c r="X26" s="8" t="inlineStr"/>
+      <c r="Y26" s="8" t="inlineStr"/>
+      <c r="Z26" s="8" t="inlineStr"/>
+      <c r="AA26" s="8" t="inlineStr"/>
+      <c r="AB26" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC26" s="8" t="inlineStr">
+        <is>
+          <t>📦広告なし</t>
+        </is>
+      </c>
+      <c r="AD26" s="5" t="inlineStr">
+        <is>
+          <t>広告費ゼロ。利益=売上−原価</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>姿勢サポートベルト</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="15" t="inlineStr"/>
-      <c r="G25" s="15" t="inlineStr"/>
-      <c r="H25" s="15" t="inlineStr"/>
-      <c r="I25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="15" t="inlineStr"/>
-      <c r="N25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="15" t="inlineStr"/>
-      <c r="S25" s="16" t="n">
+      <c r="B27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="20" t="inlineStr"/>
+      <c r="I27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="20" t="inlineStr"/>
+      <c r="N27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="20" t="inlineStr"/>
+      <c r="S27" s="21" t="n">
         <v>4551</v>
       </c>
-      <c r="T25" s="15" t="inlineStr"/>
-      <c r="U25" s="15" t="inlineStr"/>
-      <c r="V25" s="15" t="inlineStr"/>
-      <c r="W25" s="15" t="inlineStr"/>
-      <c r="X25" s="15" t="inlineStr"/>
-      <c r="Y25" s="15" t="inlineStr">
+      <c r="T27" s="20" t="inlineStr"/>
+      <c r="U27" s="20" t="inlineStr"/>
+      <c r="V27" s="20" t="inlineStr"/>
+      <c r="W27" s="20" t="inlineStr"/>
+      <c r="X27" s="20" t="inlineStr"/>
+      <c r="Y27" s="20" t="inlineStr"/>
+      <c r="Z27" s="20" t="inlineStr"/>
+      <c r="AA27" s="20" t="inlineStr"/>
+      <c r="AB27" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z25" s="15" t="inlineStr">
+      <c r="AC27" s="20" t="inlineStr">
         <is>
           <t>📦広告なし</t>
         </is>
       </c>
-      <c r="AA25" s="19" t="inlineStr">
+      <c r="AD27" s="24" t="inlineStr">
         <is>
           <t>広告費ゼロ。利益=売上−原価</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>ナノバブルシャワーヘッド</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="4" t="inlineStr"/>
-      <c r="S26" s="6" t="n">
-        <v>51975</v>
-      </c>
-      <c r="T26" s="4" t="inlineStr"/>
-      <c r="U26" s="4" t="inlineStr"/>
-      <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="4" t="inlineStr"/>
-      <c r="X26" s="4" t="inlineStr"/>
-      <c r="Y26" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>癒しの指圧マット</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="8" t="inlineStr"/>
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr"/>
+      <c r="I28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="8" t="inlineStr"/>
+      <c r="N28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="8" t="inlineStr"/>
+      <c r="S28" s="10" t="n">
+        <v>4332</v>
+      </c>
+      <c r="T28" s="8" t="inlineStr"/>
+      <c r="U28" s="8" t="inlineStr"/>
+      <c r="V28" s="8" t="inlineStr"/>
+      <c r="W28" s="8" t="inlineStr"/>
+      <c r="X28" s="8" t="inlineStr"/>
+      <c r="Y28" s="8" t="inlineStr"/>
+      <c r="Z28" s="8" t="inlineStr"/>
+      <c r="AA28" s="8" t="inlineStr"/>
+      <c r="AB28" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z26" s="4" t="inlineStr">
+      <c r="AC28" s="8" t="inlineStr">
         <is>
           <t>📦広告なし</t>
         </is>
       </c>
-      <c r="AA26" s="14" t="inlineStr">
-        <is>
-          <t>広告費ゼロ。利益=売上−原価</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>リカバリーサンダル</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="15" t="inlineStr"/>
-      <c r="G27" s="15" t="inlineStr"/>
-      <c r="H27" s="15" t="inlineStr"/>
-      <c r="I27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="15" t="inlineStr"/>
-      <c r="N27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="15" t="inlineStr"/>
-      <c r="S27" s="16" t="n">
-        <v>18697</v>
-      </c>
-      <c r="T27" s="15" t="inlineStr"/>
-      <c r="U27" s="15" t="inlineStr"/>
-      <c r="V27" s="15" t="inlineStr"/>
-      <c r="W27" s="15" t="inlineStr"/>
-      <c r="X27" s="15" t="inlineStr"/>
-      <c r="Y27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z27" s="15" t="inlineStr">
-        <is>
-          <t>📦広告なし</t>
-        </is>
-      </c>
-      <c r="AA27" s="19" t="inlineStr">
-        <is>
-          <t>広告費ゼロ。利益=売上−原価</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>癒しの指圧マット</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="4" t="inlineStr"/>
-      <c r="S28" s="6" t="n">
-        <v>4332</v>
-      </c>
-      <c r="T28" s="4" t="inlineStr"/>
-      <c r="U28" s="4" t="inlineStr"/>
-      <c r="V28" s="4" t="inlineStr"/>
-      <c r="W28" s="4" t="inlineStr"/>
-      <c r="X28" s="4" t="inlineStr"/>
-      <c r="Y28" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z28" s="4" t="inlineStr">
-        <is>
-          <t>📦広告なし</t>
-        </is>
-      </c>
-      <c r="AA28" s="14" t="inlineStr">
+      <c r="AD28" s="5" t="inlineStr">
         <is>
           <t>広告費ゼロ。利益=売上−原価</t>
         </is>
@@ -3552,7 +4689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3578,1500 +4715,1500 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>予算増減・CR投入の判定フロー　※商品別シートの判定はこのフローから機械的に生成している</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>【予算フロー】上から順に判定する</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>S-1</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>今日が この商品の判定日 か？</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>NO→据置（監視のみ）。判定日以外に予算を触らない ／ YES→S0へ　※例外: 事故（購入ゼロで分岐CPA×3を消化・CPM2倍）は即日対応</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>S0</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>日販10個未満か？</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>YES→利益率では判断しない。7日累計の金額とMERだけで判断する（日次のブレが13〜64ptあるため）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>7日利益 &gt; 0 か？</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>NO→撤退プロトコル(S1a)へ ／ YES→S2へ</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>S1a</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>日次赤字 ÷ 予算 ≥ 15%、またはテコ入れ2巡目か？</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>YES→予算半減＋テコ入れ ／ NO→予算据置＋CR追加し7日後に判定</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>MER ≥ その商品の目標MER か？</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>目標MER = 1÷(1−原価率−0.35)。商品ごとに2.17〜5.49と差が大きい。NO→S2aへ ／ YES→S3へ</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>S2a</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>余裕（MER−分岐）&gt; 0 か？</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>NO→【D:原因分解】へ（いきなり減額しない） ／ YES→S2bへ</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>S2b</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>その予算を「目標MER超え×消化率95%以上」の商品に回した方が利益が大きいか？</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>転用先の増収は**実測の増分MER**で評価する（平均MERで評価しない。平均MERは既存売上に支えられており、追加1円の成績ではない）。転用先の増分MERが実測されていない、または実測値が転用先の分岐MERを下回るなら『回しても増えない』＝転用しない。YES→停止して転用 ／ NO→維持し、CR・LP・価格で手当て</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>直近2日の消化率 ≥ 95% か？</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>NO→枠が余っている。増額しても消化できない→据置 ／ YES→S4へ（枠で止まっている）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>増分MERを測定済みか？</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>未測定→+25%増額（機会を取りにいくと同時に測定可能にする） ／ 測定済→S5へ</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>増分MER と しきい値の比較</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>≥目標MER→+20〜30%増額 ／ 分岐≤増分&lt;目標→据置（利益は増えるが利益率が下がる） ／ &lt;分岐→元の予算に戻す</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>【D:原因分解】減額の前に必ず実施。週次のCTR/CVR/CPM/頻度を前週と比べる</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>CTRの2週間累積変化が −15%以下か？（連続低下だけでは判定しない）</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>→素材疲弊。**その広告セットに新CRを追加**する。既存CRは止めない（同一セット内はMetaが自動配分するため）。予算は据置し7日後に再判定</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>D1b</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>その広告セットで配信されているCRが1本だけか？</t>
         </is>
       </c>
-      <c r="C17" s="27" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
         <is>
           <t>→疲弊が起きたときに受け皿がない。CTR劣化がなくても、日予算の大きいセットから順に**予備CRを1本足しておく**（予算・既存CRは触らない）</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>頻度 &gt; 2.5 か？</t>
         </is>
       </c>
-      <c r="C18" s="27" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>→疲弊確定。①オーディエンス拡大（類似%↑/全開放）②新CR③配信面を広げる。**予算は据置**</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>CVR（購入÷アウトバウンドクリック）が前週比 −15%以下か？</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C19" s="32" t="inlineStr">
         <is>
           <t>→LP/オファーの問題。①LP改善（FV・レビュー・配送日数）②価格/送料訴求③優先配送の見せ方。**予算は据置**</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>CPMが前週比 +15%以上か？</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C20" s="32" t="inlineStr">
         <is>
           <t>→①全開放(Advantage+)②配信面の偏り確認③訴求替えCR④値上げで高CPMを回収できる経済性にする</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>CTR・CVR・CPMすべて横ばいでCPAだけ悪化か？</t>
         </is>
       </c>
-      <c r="C21" s="27" t="inlineStr">
+      <c r="C21" s="32" t="inlineStr">
         <is>
           <t>→需要減衰。CRでは直らない。**ここで初めて減額**。季節終盤なら段階縮小</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>【CRフロー】予算フローとは独立に判定する</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>悪化の先行指標が出ているか？</t>
         </is>
       </c>
-      <c r="C24" s="27" t="inlineStr">
+      <c r="C24" s="32" t="inlineStr">
         <is>
           <t>頻度&gt;2.5 ／ CTR2週連続低下 ／ 余裕3日連続縮小 ／ 7日利益2週連続減。NO→健全な商品はCRも触らない</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>新素材はあるか？</t>
         </is>
       </c>
-      <c r="C25" s="27" t="inlineStr">
+      <c r="C25" s="32" t="inlineStr">
         <is>
           <t>YES→既存広告セットに追加し判定日を+7日リセット ／ NO→複製リセット・価格・オーディエンス替えで代替</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>【増分MERの算出】Δ売上(曜日補正後) ÷ Δ広告費</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>V1</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>|Δ広告費| ≥ 3,000円/日 か？</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr">
+      <c r="C28" s="32" t="inlineStr">
         <is>
           <t>未満は分母が小さく値が発散するため測定しない</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>V2</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B29" s="31" t="inlineStr">
         <is>
           <t>予算を意図的に変えたか？</t>
         </is>
       </c>
-      <c r="C29" s="27" t="inlineStr">
+      <c r="C29" s="32" t="inlineStr">
         <is>
           <t>変えていない場合、消化の増減はMetaのペーシング。成績が悪い日に自動で絞る逆因果を含むため実験にならない</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>V3</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>P1・P2とも予算変更日をまたいでいないか？</t>
         </is>
       </c>
-      <c r="C30" s="27" t="inlineStr">
+      <c r="C30" s="32" t="inlineStr">
         <is>
           <t>またぐと変更前後が混ざり測定にならない</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>V4</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>曜日構成を補正したか？</t>
         </is>
       </c>
-      <c r="C31" s="27" t="inlineStr">
+      <c r="C31" s="32" t="inlineStr">
         <is>
           <t>P1とP2の曜日指数の平均比で後期間の売上を補正する。補正しないと結論が反転する</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>■ 本日の全商品トレース（どの分岐を通ってその結論になったか）</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>商品</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>日販</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>7日利益</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>MER</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>目標MER</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>分岐</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>余裕</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>消化率</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>増分MER</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>判定日</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>現予算</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>提案予算</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>結論</t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>通った分岐</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>4WAY 取り付けOK 小型瞬間冷却ハンディファン</t>
         </is>
       </c>
-      <c r="B36" s="28" t="n">
+      <c r="B36" s="33" t="n">
         <v>64.3</v>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C36" s="10" t="n">
         <v>861832</v>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="D36" s="16" t="n">
         <v>3.73</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="16" t="n">
         <v>3.3</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="F36" s="16" t="n">
         <v>1.53</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="G36" s="16" t="n">
         <v>2.2</v>
       </c>
-      <c r="H36" s="29" t="n">
+      <c r="H36" s="34" t="n">
         <v>1.033</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="I36" s="16" t="n">
         <v>-3.38</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="J36" s="8" t="inlineStr">
         <is>
           <t>7/28</t>
         </is>
       </c>
-      <c r="K36" s="6" t="n">
+      <c r="K36" s="10" t="n">
         <v>95000</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="L36" s="10" t="n">
         <v>95000</v>
       </c>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="M36" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N36" s="14" t="inlineStr">
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/28）</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>害虫ブロッカー</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="35" t="n">
         <v>54</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="21" t="n">
         <v>662071</v>
       </c>
-      <c r="D37" s="18" t="n">
+      <c r="D37" s="23" t="n">
         <v>2.91</v>
       </c>
-      <c r="E37" s="18" t="n">
+      <c r="E37" s="23" t="n">
         <v>2.31</v>
       </c>
-      <c r="F37" s="18" t="n">
+      <c r="F37" s="23" t="n">
         <v>1.28</v>
       </c>
-      <c r="G37" s="18" t="n">
+      <c r="G37" s="23" t="n">
         <v>1.63</v>
       </c>
-      <c r="H37" s="31" t="n">
+      <c r="H37" s="36" t="n">
         <v>1.004</v>
       </c>
-      <c r="I37" s="15" t="inlineStr">
+      <c r="I37" s="20" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J37" s="15" t="inlineStr">
+      <c r="J37" s="20" t="inlineStr">
         <is>
           <t>7/30</t>
         </is>
       </c>
-      <c r="K37" s="16" t="n">
+      <c r="K37" s="21" t="n">
         <v>85000</v>
       </c>
-      <c r="L37" s="16" t="n">
+      <c r="L37" s="21" t="n">
         <v>85000</v>
       </c>
-      <c r="M37" s="15" t="inlineStr">
+      <c r="M37" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N37" s="19" t="inlineStr">
+      <c r="N37" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/30）</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>形状記憶日傘</t>
         </is>
       </c>
-      <c r="B38" s="28" t="n">
+      <c r="B38" s="33" t="n">
         <v>41.9</v>
       </c>
-      <c r="C38" s="6" t="n">
+      <c r="C38" s="10" t="n">
         <v>652037</v>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D38" s="16" t="n">
         <v>3.44</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="16" t="n">
         <v>2.58</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="16" t="n">
         <v>1.36</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="G38" s="16" t="n">
         <v>2.08</v>
       </c>
-      <c r="H38" s="29" t="n">
+      <c r="H38" s="34" t="n">
         <v>0.983</v>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="J38" s="8" t="inlineStr">
         <is>
           <t>なし(健全)</t>
         </is>
       </c>
-      <c r="K38" s="6" t="n">
+      <c r="K38" s="10" t="n">
         <v>60000</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="L38" s="10" t="n">
         <v>60000</v>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="M38" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N38" s="14" t="inlineStr">
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 なし(健全)）</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>ナノガラス脱毛パッド</t>
         </is>
       </c>
-      <c r="B39" s="30" t="n">
+      <c r="B39" s="35" t="n">
         <v>35.3</v>
       </c>
-      <c r="C39" s="16" t="n">
+      <c r="C39" s="21" t="n">
         <v>405323</v>
       </c>
-      <c r="D39" s="18" t="n">
+      <c r="D39" s="23" t="n">
         <v>2.51</v>
       </c>
-      <c r="E39" s="18" t="n">
+      <c r="E39" s="23" t="n">
         <v>2.17</v>
       </c>
-      <c r="F39" s="18" t="n">
+      <c r="F39" s="23" t="n">
         <v>1.23</v>
       </c>
-      <c r="G39" s="18" t="n">
+      <c r="G39" s="23" t="n">
         <v>1.28</v>
       </c>
-      <c r="H39" s="31" t="n">
+      <c r="H39" s="36" t="n">
         <v>1.002</v>
       </c>
-      <c r="I39" s="15" t="inlineStr">
+      <c r="I39" s="20" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J39" s="15" t="inlineStr">
+      <c r="J39" s="20" t="inlineStr">
         <is>
           <t>7/30</t>
         </is>
       </c>
-      <c r="K39" s="16" t="n">
+      <c r="K39" s="21" t="n">
         <v>68000</v>
       </c>
-      <c r="L39" s="16" t="n">
+      <c r="L39" s="21" t="n">
         <v>68000</v>
       </c>
-      <c r="M39" s="15" t="inlineStr">
+      <c r="M39" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N39" s="19" t="inlineStr">
+      <c r="N39" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/30）</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>卓上冷感クーラー</t>
         </is>
       </c>
-      <c r="B40" s="33" t="n">
+      <c r="B40" s="37" t="n">
         <v>18.9</v>
       </c>
-      <c r="C40" s="34" t="n">
+      <c r="C40" s="38" t="n">
         <v>314207</v>
       </c>
-      <c r="D40" s="35" t="n">
+      <c r="D40" s="39" t="n">
         <v>3.73</v>
       </c>
-      <c r="E40" s="35" t="n">
+      <c r="E40" s="39" t="n">
         <v>3.16</v>
       </c>
-      <c r="F40" s="35" t="n">
+      <c r="F40" s="39" t="n">
         <v>1.5</v>
       </c>
-      <c r="G40" s="35" t="n">
+      <c r="G40" s="39" t="n">
         <v>2.23</v>
       </c>
-      <c r="H40" s="36" t="n">
+      <c r="H40" s="40" t="n">
         <v>0.982</v>
       </c>
-      <c r="I40" s="35" t="n">
+      <c r="I40" s="39" t="n">
         <v>-9.539999999999999</v>
       </c>
-      <c r="J40" s="32" t="inlineStr">
+      <c r="J40" s="19" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K40" s="34" t="n">
+      <c r="K40" s="38" t="n">
         <v>38000</v>
       </c>
-      <c r="L40" s="34" t="n">
+      <c r="L40" s="38" t="n">
         <v>30000</v>
       </c>
-      <c r="M40" s="32" t="inlineStr">
+      <c r="M40" s="19" t="inlineStr">
         <is>
           <t>🚨 元の予算に戻す</t>
         </is>
       </c>
-      <c r="N40" s="37" t="inlineStr">
+      <c r="N40" s="41" t="inlineStr">
         <is>
           <t>S-1:本日が判定日 → S0:日販18.9個 → S1:7日利益+314,207円→黒字 → S2:MER 3.73 ≥ 目標 3.16→効率OK → S3:消化率98%≥95%→枠で止まっている → S4:増分MER測定済 -9.54 → S5:-9.54 &lt; 分岐1.50→増額分が赤字</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>完全遮光・形状記憶・晴雨兼用・UV日傘</t>
         </is>
       </c>
-      <c r="B41" s="30" t="n">
+      <c r="B41" s="35" t="n">
         <v>19.6</v>
       </c>
-      <c r="C41" s="16" t="n">
+      <c r="C41" s="21" t="n">
         <v>241237</v>
       </c>
-      <c r="D41" s="18" t="n">
+      <c r="D41" s="23" t="n">
         <v>2.55</v>
       </c>
-      <c r="E41" s="18" t="n">
+      <c r="E41" s="23" t="n">
         <v>2.56</v>
       </c>
-      <c r="F41" s="18" t="n">
+      <c r="F41" s="23" t="n">
         <v>1.35</v>
       </c>
-      <c r="G41" s="18" t="n">
+      <c r="G41" s="23" t="n">
         <v>1.2</v>
       </c>
-      <c r="H41" s="31" t="n">
+      <c r="H41" s="36" t="n">
         <v>0.997</v>
       </c>
-      <c r="I41" s="18" t="n">
+      <c r="I41" s="23" t="n">
         <v>-7.92</v>
       </c>
-      <c r="J41" s="15" t="inlineStr">
+      <c r="J41" s="20" t="inlineStr">
         <is>
           <t>7/28</t>
         </is>
       </c>
-      <c r="K41" s="16" t="n">
+      <c r="K41" s="21" t="n">
         <v>41000</v>
       </c>
-      <c r="L41" s="16" t="n">
+      <c r="L41" s="21" t="n">
         <v>41000</v>
       </c>
-      <c r="M41" s="15" t="inlineStr">
+      <c r="M41" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N41" s="19" t="inlineStr">
+      <c r="N41" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/28）</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>接触冷感UVパーカー</t>
         </is>
       </c>
-      <c r="B42" s="28" t="n">
+      <c r="B42" s="33" t="n">
         <v>23.7</v>
       </c>
-      <c r="C42" s="6" t="n">
+      <c r="C42" s="10" t="n">
         <v>201231</v>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="D42" s="16" t="n">
         <v>2.98</v>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="16" t="n">
         <v>3.45</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="F42" s="16" t="n">
         <v>1.56</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="G42" s="16" t="n">
         <v>1.42</v>
       </c>
-      <c r="H42" s="29" t="n">
+      <c r="H42" s="34" t="n">
         <v>1.024</v>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>7/28</t>
         </is>
       </c>
-      <c r="K42" s="6" t="n">
+      <c r="K42" s="10" t="n">
         <v>34000</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="L42" s="10" t="n">
         <v>34000</v>
       </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="M42" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N42" s="14" t="inlineStr">
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/28）</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>5WAY腰掛けファン</t>
         </is>
       </c>
-      <c r="B43" s="30" t="n">
+      <c r="B43" s="35" t="n">
         <v>11.6</v>
       </c>
-      <c r="C43" s="16" t="n">
+      <c r="C43" s="21" t="n">
         <v>165862</v>
       </c>
-      <c r="D43" s="18" t="n">
+      <c r="D43" s="23" t="n">
         <v>4.59</v>
       </c>
-      <c r="E43" s="18" t="n">
+      <c r="E43" s="23" t="n">
         <v>3.59</v>
       </c>
-      <c r="F43" s="18" t="n">
+      <c r="F43" s="23" t="n">
         <v>1.59</v>
       </c>
-      <c r="G43" s="18" t="n">
+      <c r="G43" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="31" t="n">
+      <c r="H43" s="36" t="n">
         <v>1.018</v>
       </c>
-      <c r="I43" s="15" t="inlineStr">
+      <c r="I43" s="20" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J43" s="15" t="inlineStr">
+      <c r="J43" s="20" t="inlineStr">
         <is>
           <t>7/28</t>
         </is>
       </c>
-      <c r="K43" s="16" t="n">
+      <c r="K43" s="21" t="n">
         <v>13000</v>
       </c>
-      <c r="L43" s="16" t="n">
+      <c r="L43" s="21" t="n">
         <v>13000</v>
       </c>
-      <c r="M43" s="15" t="inlineStr">
+      <c r="M43" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N43" s="19" t="inlineStr">
+      <c r="N43" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/28）</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>3WAYサーキュレーター扇風機</t>
         </is>
       </c>
-      <c r="B44" s="28" t="n">
+      <c r="B44" s="33" t="n">
         <v>7.4</v>
       </c>
-      <c r="C44" s="6" t="n">
+      <c r="C44" s="10" t="n">
         <v>77095</v>
       </c>
-      <c r="D44" s="12" t="n">
+      <c r="D44" s="16" t="n">
         <v>2.97</v>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="16" t="n">
         <v>4.27</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="F44" s="16" t="n">
         <v>1.71</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="G44" s="16" t="n">
         <v>1.26</v>
       </c>
-      <c r="H44" s="29" t="n">
+      <c r="H44" s="34" t="n">
         <v>1.02</v>
       </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>7/29</t>
         </is>
       </c>
-      <c r="K44" s="6" t="n">
+      <c r="K44" s="10" t="n">
         <v>16000</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="L44" s="10" t="n">
         <v>16000</v>
       </c>
-      <c r="M44" s="4" t="inlineStr">
+      <c r="M44" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N44" s="14" t="inlineStr">
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/29）</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>偏光・調光サングラス</t>
         </is>
       </c>
-      <c r="B45" s="30" t="n">
+      <c r="B45" s="35" t="n">
         <v>10.1</v>
       </c>
-      <c r="C45" s="16" t="n">
+      <c r="C45" s="21" t="n">
         <v>65471</v>
       </c>
-      <c r="D45" s="18" t="n">
+      <c r="D45" s="23" t="n">
         <v>1.84</v>
       </c>
-      <c r="E45" s="18" t="n">
+      <c r="E45" s="23" t="n">
         <v>2.35</v>
       </c>
-      <c r="F45" s="18" t="n">
+      <c r="F45" s="23" t="n">
         <v>1.29</v>
       </c>
-      <c r="G45" s="18" t="n">
+      <c r="G45" s="23" t="n">
         <v>0.55</v>
       </c>
-      <c r="H45" s="31" t="n">
+      <c r="H45" s="36" t="n">
         <v>0.982</v>
       </c>
-      <c r="I45" s="15" t="inlineStr">
+      <c r="I45" s="20" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J45" s="15" t="inlineStr">
+      <c r="J45" s="20" t="inlineStr">
         <is>
           <t>7/29</t>
         </is>
       </c>
-      <c r="K45" s="16" t="n">
+      <c r="K45" s="21" t="n">
         <v>22000</v>
       </c>
-      <c r="L45" s="16" t="n">
+      <c r="L45" s="21" t="n">
         <v>22000</v>
       </c>
-      <c r="M45" s="15" t="inlineStr">
+      <c r="M45" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N45" s="19" t="inlineStr">
+      <c r="N45" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/29）</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>ムダ毛シェーバー</t>
         </is>
       </c>
-      <c r="B46" s="28" t="n">
+      <c r="B46" s="33" t="n">
         <v>6.4</v>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="C46" s="10" t="n">
         <v>49585</v>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="D46" s="16" t="n">
         <v>2.87</v>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="16" t="n">
         <v>5.49</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="F46" s="16" t="n">
         <v>1.88</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="G46" s="16" t="n">
         <v>0.99</v>
       </c>
-      <c r="H46" s="29" t="n">
+      <c r="H46" s="34" t="n">
         <v>1.067</v>
       </c>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K46" s="6" t="n">
+      <c r="K46" s="10" t="n">
         <v>13000</v>
       </c>
-      <c r="L46" s="6" t="n">
+      <c r="L46" s="10" t="n">
         <v>13000</v>
       </c>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="M46" s="8" t="inlineStr">
         <is>
           <t>✅ 維持（CR/LP/価格で手当て）</t>
         </is>
       </c>
-      <c r="N46" s="14" t="inlineStr">
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>S-1:本日が判定日 → S0:日販6.4個（&lt;10 利益率は参考値扱い） → S1:7日利益+49,585円→黒字 → S2:MER 2.87 &lt; 目標 5.49 → S2a:余裕+0.99&gt;0 → S2b:転用先候補（害虫2.91/ナノ2.51/4WAY3.73）はいずれも直近の増額分の増分MERが未測定または分岐割れ。平均MERで転用益を見積もらない→維持</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>接触冷感UVアームカバー</t>
         </is>
       </c>
-      <c r="B47" s="30" t="n">
+      <c r="B47" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="21" t="n">
         <v>80892</v>
       </c>
-      <c r="D47" s="18" t="n">
+      <c r="D47" s="23" t="n">
         <v>2.08</v>
       </c>
-      <c r="E47" s="18" t="n">
+      <c r="E47" s="23" t="n">
         <v>2.21</v>
       </c>
-      <c r="F47" s="18" t="n">
+      <c r="F47" s="23" t="n">
         <v>1.25</v>
       </c>
-      <c r="G47" s="18" t="n">
+      <c r="G47" s="23" t="n">
         <v>0.83</v>
       </c>
-      <c r="H47" s="31" t="n">
+      <c r="H47" s="36" t="n">
         <v>1.035</v>
       </c>
-      <c r="I47" s="15" t="inlineStr">
+      <c r="I47" s="20" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J47" s="15" t="inlineStr">
+      <c r="J47" s="20" t="inlineStr">
         <is>
           <t>7/29</t>
         </is>
       </c>
-      <c r="K47" s="16" t="n">
+      <c r="K47" s="21" t="n">
         <v>17000</v>
       </c>
-      <c r="L47" s="16" t="n">
+      <c r="L47" s="21" t="n">
         <v>17000</v>
       </c>
-      <c r="M47" s="15" t="inlineStr">
+      <c r="M47" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N47" s="19" t="inlineStr">
+      <c r="N47" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/29）</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>瞬間冷感ポンチョ</t>
         </is>
       </c>
-      <c r="B48" s="28" t="n">
+      <c r="B48" s="33" t="n">
         <v>7.3</v>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C48" s="10" t="n">
         <v>59853</v>
       </c>
-      <c r="D48" s="12" t="n">
+      <c r="D48" s="16" t="n">
         <v>2.19</v>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="16" t="n">
         <v>2.49</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="F48" s="16" t="n">
         <v>1.33</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="G48" s="16" t="n">
         <v>0.86</v>
       </c>
-      <c r="H48" s="29" t="n">
+      <c r="H48" s="34" t="n">
         <v>1.015</v>
       </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="J48" s="8" t="inlineStr">
         <is>
           <t>8/1</t>
         </is>
       </c>
-      <c r="K48" s="6" t="n">
+      <c r="K48" s="10" t="n">
         <v>13000</v>
       </c>
-      <c r="L48" s="6" t="n">
+      <c r="L48" s="10" t="n">
         <v>13000</v>
       </c>
-      <c r="M48" s="4" t="inlineStr">
+      <c r="M48" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N48" s="14" t="inlineStr">
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 8/1）</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>健康サンダル</t>
         </is>
       </c>
-      <c r="B49" s="30" t="n">
+      <c r="B49" s="35" t="n">
         <v>5.3</v>
       </c>
-      <c r="C49" s="16" t="n">
+      <c r="C49" s="21" t="n">
         <v>58635</v>
       </c>
-      <c r="D49" s="18" t="n">
+      <c r="D49" s="23" t="n">
         <v>2.1</v>
       </c>
-      <c r="E49" s="18" t="n">
+      <c r="E49" s="23" t="n">
         <v>2.33</v>
       </c>
-      <c r="F49" s="18" t="n">
+      <c r="F49" s="23" t="n">
         <v>1.28</v>
       </c>
-      <c r="G49" s="18" t="n">
+      <c r="G49" s="23" t="n">
         <v>0.82</v>
       </c>
-      <c r="H49" s="31" t="n">
+      <c r="H49" s="36" t="n">
         <v>1.062</v>
       </c>
-      <c r="I49" s="15" t="inlineStr">
+      <c r="I49" s="20" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J49" s="15" t="inlineStr">
+      <c r="J49" s="20" t="inlineStr">
         <is>
           <t>なし(健全)</t>
         </is>
       </c>
-      <c r="K49" s="16" t="n">
+      <c r="K49" s="21" t="n">
         <v>13000</v>
       </c>
-      <c r="L49" s="16" t="n">
+      <c r="L49" s="21" t="n">
         <v>13000</v>
       </c>
-      <c r="M49" s="15" t="inlineStr">
+      <c r="M49" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N49" s="19" t="inlineStr">
+      <c r="N49" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 なし(健全)）</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>UV歯ブラシ除菌器</t>
         </is>
       </c>
-      <c r="B50" s="28" t="n">
+      <c r="B50" s="33" t="n">
         <v>2.6</v>
       </c>
-      <c r="C50" s="6" t="n">
+      <c r="C50" s="10" t="n">
         <v>26516</v>
       </c>
-      <c r="D50" s="12" t="n">
+      <c r="D50" s="16" t="n">
         <v>2.1</v>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="16" t="n">
         <v>3.46</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="F50" s="16" t="n">
         <v>1.56</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="G50" s="16" t="n">
         <v>0.54</v>
       </c>
-      <c r="H50" s="29" t="n">
+      <c r="H50" s="34" t="n">
         <v>0.925</v>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="J50" s="8" t="inlineStr">
         <is>
           <t>7/30</t>
         </is>
       </c>
-      <c r="K50" s="6" t="n">
+      <c r="K50" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="L50" s="6" t="n">
+      <c r="L50" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="M50" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N50" s="14" t="inlineStr">
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/30）</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>携帯電動シェーバー</t>
         </is>
       </c>
-      <c r="B51" s="30" t="n">
+      <c r="B51" s="35" t="n">
         <v>3.9</v>
       </c>
-      <c r="C51" s="16" t="n">
+      <c r="C51" s="21" t="n">
         <v>14638</v>
       </c>
-      <c r="D51" s="18" t="n">
+      <c r="D51" s="23" t="n">
         <v>1.79</v>
       </c>
-      <c r="E51" s="18" t="n">
+      <c r="E51" s="23" t="n">
         <v>3.2</v>
       </c>
-      <c r="F51" s="18" t="n">
+      <c r="F51" s="23" t="n">
         <v>1.51</v>
       </c>
-      <c r="G51" s="18" t="n">
+      <c r="G51" s="23" t="n">
         <v>0.28</v>
       </c>
-      <c r="H51" s="31" t="n">
+      <c r="H51" s="36" t="n">
         <v>1.03</v>
       </c>
-      <c r="I51" s="15" t="inlineStr">
+      <c r="I51" s="20" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J51" s="15" t="inlineStr">
+      <c r="J51" s="20" t="inlineStr">
         <is>
           <t>8/1</t>
         </is>
       </c>
-      <c r="K51" s="16" t="n">
+      <c r="K51" s="21" t="n">
         <v>11000</v>
       </c>
-      <c r="L51" s="16" t="n">
+      <c r="L51" s="21" t="n">
         <v>11000</v>
       </c>
-      <c r="M51" s="15" t="inlineStr">
+      <c r="M51" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N51" s="19" t="inlineStr">
+      <c r="N51" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 8/1）</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>バランスケアスリッパ</t>
         </is>
       </c>
-      <c r="B52" s="28" t="n">
+      <c r="B52" s="33" t="n">
         <v>2.6</v>
       </c>
-      <c r="C52" s="6" t="n">
+      <c r="C52" s="10" t="n">
         <v>18274</v>
       </c>
-      <c r="D52" s="12" t="n">
+      <c r="D52" s="16" t="n">
         <v>1.87</v>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="16" t="n">
         <v>2.58</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="F52" s="16" t="n">
         <v>1.35</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="G52" s="16" t="n">
         <v>0.52</v>
       </c>
-      <c r="H52" s="29" t="n">
+      <c r="H52" s="34" t="n">
         <v>0.98</v>
       </c>
-      <c r="I52" s="12" t="n">
+      <c r="I52" s="16" t="n">
         <v>0.91</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>7/29</t>
         </is>
       </c>
-      <c r="K52" s="6" t="n">
+      <c r="K52" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="L52" s="6" t="n">
+      <c r="L52" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="M52" s="4" t="inlineStr">
+      <c r="M52" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N52" s="14" t="inlineStr">
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/29）</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>壁掛けディスペンサー</t>
         </is>
       </c>
-      <c r="B53" s="30" t="n">
+      <c r="B53" s="35" t="n">
         <v>1.6</v>
       </c>
-      <c r="C53" s="16" t="n">
+      <c r="C53" s="21" t="n">
         <v>-16403</v>
       </c>
-      <c r="D53" s="18" t="n">
+      <c r="D53" s="23" t="n">
         <v>1.11</v>
       </c>
-      <c r="E53" s="18" t="n">
+      <c r="E53" s="23" t="n">
         <v>2.77</v>
       </c>
-      <c r="F53" s="18" t="n">
+      <c r="F53" s="23" t="n">
         <v>1.41</v>
       </c>
-      <c r="G53" s="18" t="n">
+      <c r="G53" s="23" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H53" s="31" t="n">
+      <c r="H53" s="36" t="n">
         <v>1.452</v>
       </c>
-      <c r="I53" s="18" t="n">
+      <c r="I53" s="23" t="n">
         <v>0.36</v>
       </c>
-      <c r="J53" s="15" t="inlineStr">
+      <c r="J53" s="20" t="inlineStr">
         <is>
           <t>8/1</t>
         </is>
       </c>
-      <c r="K53" s="16" t="n">
+      <c r="K53" s="21" t="n">
         <v>6000</v>
       </c>
-      <c r="L53" s="16" t="n">
+      <c r="L53" s="21" t="n">
         <v>6000</v>
       </c>
-      <c r="M53" s="15" t="inlineStr">
+      <c r="M53" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N53" s="19" t="inlineStr">
+      <c r="N53" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 8/1）</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>湯上がりガーゼワンピース</t>
         </is>
       </c>
-      <c r="B54" s="28" t="n">
+      <c r="B54" s="33" t="n">
         <v>1.7</v>
       </c>
-      <c r="C54" s="6" t="n">
+      <c r="C54" s="10" t="n">
         <v>6076</v>
       </c>
-      <c r="D54" s="12" t="n">
+      <c r="D54" s="16" t="n">
         <v>1.71</v>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="16" t="n">
         <v>3.12</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="F54" s="16" t="n">
         <v>1.49</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="G54" s="16" t="n">
         <v>0.22</v>
       </c>
-      <c r="H54" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="H54" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr"/>
-      <c r="K54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr"/>
+      <c r="K54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="8" t="inlineStr">
         <is>
           <t>⏹ 停止済み</t>
         </is>
       </c>
-      <c r="N54" s="14" t="inlineStr">
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>S-1:7/26に停止（S2b 機会費用）済み。以後は判定対象外</t>
         </is>
